--- a/source/8、绩效异常岗位/3、倒包岗/倒包岗-6月.xlsx
+++ b/source/8、绩效异常岗位/3、倒包岗/倒包岗-6月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="79">
   <si>
     <t>数据日期</t>
   </si>
@@ -64,33 +64,21 @@
     <t>石家庄</t>
   </si>
   <si>
-    <t>80.7</t>
-  </si>
-  <si>
     <t>河南区</t>
   </si>
   <si>
     <t>商丘</t>
   </si>
   <si>
-    <t>88.4</t>
-  </si>
-  <si>
     <t>肃宁</t>
   </si>
   <si>
-    <t>92.3</t>
-  </si>
-  <si>
     <t>江苏区</t>
   </si>
   <si>
     <t>淮安</t>
   </si>
   <si>
-    <t>81.8</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -100,96 +88,63 @@
     <t>盘锦</t>
   </si>
   <si>
-    <t>107.5</t>
-  </si>
-  <si>
     <t>山西区</t>
   </si>
   <si>
     <t>太原</t>
   </si>
   <si>
-    <t>126.9</t>
-  </si>
-  <si>
     <t>宁夏区</t>
   </si>
   <si>
     <t>银川</t>
   </si>
   <si>
-    <t>111.5</t>
-  </si>
-  <si>
     <t>湖南区</t>
   </si>
   <si>
     <t>衡阳</t>
   </si>
   <si>
-    <t>103.8</t>
-  </si>
-  <si>
     <t>天津区</t>
   </si>
   <si>
     <t>天津</t>
   </si>
   <si>
-    <t>111.9</t>
-  </si>
-  <si>
     <t>湖北区</t>
   </si>
   <si>
     <t>武汉</t>
   </si>
   <si>
-    <t>115.3</t>
-  </si>
-  <si>
     <t>贵州区</t>
   </si>
   <si>
     <t>贵阳</t>
   </si>
   <si>
-    <t>117.5</t>
-  </si>
-  <si>
     <t>浙南区</t>
   </si>
   <si>
     <t>临海</t>
   </si>
   <si>
-    <t>116.5</t>
-  </si>
-  <si>
     <t>新乡</t>
   </si>
   <si>
-    <t>105.5</t>
-  </si>
-  <si>
     <t>广东区</t>
   </si>
   <si>
     <t>东莞</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>内蒙古区</t>
   </si>
   <si>
     <t>呼和浩特</t>
   </si>
   <si>
-    <t>96.1</t>
-  </si>
-  <si>
     <t>温州</t>
   </si>
   <si>
@@ -199,9 +154,6 @@
     <t>柳州</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
     <t>浙北区</t>
   </si>
   <si>
@@ -232,18 +184,12 @@
     <t>哈尔滨</t>
   </si>
   <si>
-    <t>129.2</t>
-  </si>
-  <si>
     <t>邢邯</t>
   </si>
   <si>
     <t>义乌</t>
   </si>
   <si>
-    <t>167</t>
-  </si>
-  <si>
     <t>深圳</t>
   </si>
   <si>
@@ -253,61 +199,73 @@
     <t>临沂</t>
   </si>
   <si>
-    <t>87.6</t>
-  </si>
-  <si>
     <t>东方天地港</t>
   </si>
   <si>
-    <t>135.2</t>
-  </si>
-  <si>
     <t>襄阳</t>
   </si>
   <si>
-    <t>98.2</t>
-  </si>
-  <si>
     <t>粤东区</t>
   </si>
   <si>
     <t>揭阳</t>
   </si>
   <si>
-    <t>152.4</t>
-  </si>
-  <si>
     <t>佛山</t>
   </si>
   <si>
     <t>沈阳</t>
   </si>
   <si>
-    <t>110.9</t>
-  </si>
-  <si>
     <t>杭州</t>
   </si>
   <si>
-    <t>143.2</t>
-  </si>
-  <si>
     <t>漯河</t>
   </si>
   <si>
-    <t>134.6</t>
-  </si>
-  <si>
     <t>广州</t>
   </si>
   <si>
-    <t>155.5</t>
-  </si>
-  <si>
     <t>南京</t>
   </si>
   <si>
-    <t>146.1</t>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>荆州</t>
+  </si>
+  <si>
+    <t>长治</t>
+  </si>
+  <si>
+    <t>武昌</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>四川区</t>
+  </si>
+  <si>
+    <t>成都</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>福建区</t>
+  </si>
+  <si>
+    <t>泉州</t>
+  </si>
+  <si>
+    <t>陕西区</t>
+  </si>
+  <si>
+    <t>西安</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1277,8 +1235,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2">
+        <v>80.7</v>
       </c>
       <c r="E2">
         <v>131.7</v>
@@ -1298,13 +1256,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
+      <c r="D3">
+        <v>88.4</v>
       </c>
       <c r="E3">
         <v>140.9</v>
@@ -1327,10 +1285,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>92.3</v>
       </c>
       <c r="E4">
         <v>139.1</v>
@@ -1350,13 +1308,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>81.8</v>
       </c>
       <c r="E5">
         <v>122.9</v>
@@ -1365,10 +1323,10 @@
         <v>50.2</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1376,13 +1334,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>107.5</v>
       </c>
       <c r="E6">
         <v>157.5</v>
@@ -1402,13 +1360,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>126.9</v>
       </c>
       <c r="E7">
         <v>179.9</v>
@@ -1428,13 +1386,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>111.5</v>
       </c>
       <c r="E8">
         <v>153.6</v>
@@ -1454,13 +1412,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>103.8</v>
       </c>
       <c r="E9">
         <v>141.9</v>
@@ -1480,13 +1438,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>111.9</v>
       </c>
       <c r="E10">
         <v>152</v>
@@ -1506,13 +1464,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="D11">
+        <v>115.3</v>
       </c>
       <c r="E11">
         <v>150.9</v>
@@ -1532,13 +1490,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>117.5</v>
       </c>
       <c r="E12">
         <v>153.2</v>
@@ -1558,13 +1516,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="D13">
+        <v>116.5</v>
       </c>
       <c r="E13">
         <v>148.7</v>
@@ -1584,13 +1542,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>105.5</v>
       </c>
       <c r="E14">
         <v>133.3</v>
@@ -1610,13 +1568,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
       </c>
       <c r="E15">
         <v>125.6</v>
@@ -1625,10 +1583,10 @@
         <v>25.6</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1636,13 +1594,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
+        <v>37</v>
+      </c>
+      <c r="D16">
+        <v>96.1</v>
       </c>
       <c r="E16">
         <v>118.7</v>
@@ -1651,10 +1609,10 @@
         <v>23.4</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1662,13 +1620,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
+        <v>38</v>
+      </c>
+      <c r="D17">
+        <v>96.1</v>
       </c>
       <c r="E17">
         <v>118.2</v>
@@ -1677,10 +1635,10 @@
         <v>22.9</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1688,13 +1646,13 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="D18">
+        <v>73</v>
       </c>
       <c r="E18">
         <v>89.2</v>
@@ -1703,10 +1661,10 @@
         <v>22.1</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1714,13 +1672,13 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>126.9</v>
       </c>
       <c r="E19">
         <v>153.5</v>
@@ -1740,13 +1698,13 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>56</v>
+        <v>44</v>
+      </c>
+      <c r="D20">
+        <v>73</v>
       </c>
       <c r="E20">
         <v>88.1</v>
@@ -1755,10 +1713,10 @@
         <v>20.6</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1766,13 +1724,13 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>16</v>
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>92.3</v>
       </c>
       <c r="E21">
         <v>110.9</v>
@@ -1781,10 +1739,10 @@
         <v>20.1</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1792,13 +1750,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="D22">
+        <v>96.1</v>
       </c>
       <c r="E22">
         <v>114.6</v>
@@ -1807,10 +1765,10 @@
         <v>19.2</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1818,13 +1776,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="D23">
+        <v>88.4</v>
       </c>
       <c r="E23">
         <v>105.2</v>
@@ -1833,10 +1791,10 @@
         <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1844,13 +1802,13 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>29</v>
+        <v>48</v>
+      </c>
+      <c r="D24">
+        <v>111.5</v>
       </c>
       <c r="E24">
         <v>132.4</v>
@@ -1870,13 +1828,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>67</v>
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>129.2</v>
       </c>
       <c r="E25">
         <v>153</v>
@@ -1899,10 +1857,10 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
+        <v>51</v>
+      </c>
+      <c r="D26">
+        <v>92.3</v>
       </c>
       <c r="E26">
         <v>108.4</v>
@@ -1911,10 +1869,10 @@
         <v>17.4</v>
       </c>
       <c r="G26" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1922,13 +1880,13 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" t="s">
-        <v>70</v>
+        <v>52</v>
+      </c>
+      <c r="D27">
+        <v>167</v>
       </c>
       <c r="E27">
         <v>189.8</v>
@@ -1948,13 +1906,13 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" t="s">
-        <v>38</v>
+        <v>53</v>
+      </c>
+      <c r="D28">
+        <v>115.3</v>
       </c>
       <c r="E28">
         <v>130.4</v>
@@ -1974,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" t="s">
-        <v>74</v>
+        <v>55</v>
+      </c>
+      <c r="D29">
+        <v>87.6</v>
       </c>
       <c r="E29">
         <v>99</v>
@@ -1989,10 +1947,10 @@
         <v>12.9</v>
       </c>
       <c r="G29" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2000,13 +1958,13 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" t="s">
-        <v>76</v>
+        <v>56</v>
+      </c>
+      <c r="D30">
+        <v>135.2</v>
       </c>
       <c r="E30">
         <v>152.3</v>
@@ -2026,13 +1984,13 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" t="s">
-        <v>78</v>
+        <v>57</v>
+      </c>
+      <c r="D31">
+        <v>98.2</v>
       </c>
       <c r="E31">
         <v>109.4</v>
@@ -2041,10 +1999,10 @@
         <v>11.3</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2052,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>81</v>
+        <v>59</v>
+      </c>
+      <c r="D32">
+        <v>152.4</v>
       </c>
       <c r="E32">
         <v>169.3</v>
@@ -2078,13 +2036,13 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" t="s">
-        <v>26</v>
+        <v>60</v>
+      </c>
+      <c r="D33">
+        <v>126.9</v>
       </c>
       <c r="E33">
         <v>140.9</v>
@@ -2104,13 +2062,13 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" t="s">
-        <v>84</v>
+        <v>61</v>
+      </c>
+      <c r="D34">
+        <v>110.9</v>
       </c>
       <c r="E34">
         <v>122.4</v>
@@ -2119,10 +2077,10 @@
         <v>10.4</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2130,13 +2088,13 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>86</v>
+        <v>62</v>
+      </c>
+      <c r="D35">
+        <v>143.2</v>
       </c>
       <c r="E35">
         <v>155.4</v>
@@ -2156,13 +2114,13 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" t="s">
-        <v>88</v>
+        <v>63</v>
+      </c>
+      <c r="D36">
+        <v>134.6</v>
       </c>
       <c r="E36">
         <v>143.1</v>
@@ -2182,13 +2140,13 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" t="s">
-        <v>90</v>
+        <v>64</v>
+      </c>
+      <c r="D37">
+        <v>155.5</v>
       </c>
       <c r="E37">
         <v>163.4</v>
@@ -2208,13 +2166,13 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" t="s">
-        <v>92</v>
+        <v>65</v>
+      </c>
+      <c r="D38">
+        <v>146.1</v>
       </c>
       <c r="E38">
         <v>141</v>
@@ -2227,6 +2185,3074 @@
       </c>
       <c r="H38">
         <v>11.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39">
+        <v>88.4</v>
+      </c>
+      <c r="E39">
+        <v>155.4</v>
+      </c>
+      <c r="F39">
+        <v>75.6</v>
+      </c>
+      <c r="G39">
+        <v>123.2</v>
+      </c>
+      <c r="H39">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>80.7</v>
+      </c>
+      <c r="E40">
+        <v>109.2</v>
+      </c>
+      <c r="F40">
+        <v>35.2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41">
+        <v>100</v>
+      </c>
+      <c r="E41">
+        <v>131</v>
+      </c>
+      <c r="F41">
+        <v>31</v>
+      </c>
+      <c r="G41">
+        <v>123.2</v>
+      </c>
+      <c r="H41">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42">
+        <v>81.8</v>
+      </c>
+      <c r="E42">
+        <v>106.8</v>
+      </c>
+      <c r="F42">
+        <v>30.5</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43">
+        <v>109</v>
+      </c>
+      <c r="E43">
+        <v>141.9</v>
+      </c>
+      <c r="F43">
+        <v>30.2</v>
+      </c>
+      <c r="G43">
+        <v>123.2</v>
+      </c>
+      <c r="H43">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44">
+        <v>126.9</v>
+      </c>
+      <c r="E44">
+        <v>155.1</v>
+      </c>
+      <c r="F44">
+        <v>22.2</v>
+      </c>
+      <c r="G44">
+        <v>123.2</v>
+      </c>
+      <c r="H44">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45">
+        <v>103.8</v>
+      </c>
+      <c r="E45">
+        <v>126.3</v>
+      </c>
+      <c r="F45">
+        <v>21.6</v>
+      </c>
+      <c r="G45">
+        <v>123.2</v>
+      </c>
+      <c r="H45">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46">
+        <v>92.3</v>
+      </c>
+      <c r="E46">
+        <v>111.7</v>
+      </c>
+      <c r="F46">
+        <v>21</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47">
+        <v>111.5</v>
+      </c>
+      <c r="E47">
+        <v>134.7</v>
+      </c>
+      <c r="F47">
+        <v>20.8</v>
+      </c>
+      <c r="G47">
+        <v>123.2</v>
+      </c>
+      <c r="H47">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48">
+        <v>116.9</v>
+      </c>
+      <c r="E48">
+        <v>139.7</v>
+      </c>
+      <c r="F48">
+        <v>19.4</v>
+      </c>
+      <c r="G48">
+        <v>123.2</v>
+      </c>
+      <c r="H48">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49">
+        <v>167</v>
+      </c>
+      <c r="E49">
+        <v>198.2</v>
+      </c>
+      <c r="F49">
+        <v>18.6</v>
+      </c>
+      <c r="G49">
+        <v>123.2</v>
+      </c>
+      <c r="H49">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50">
+        <v>117.5</v>
+      </c>
+      <c r="E50">
+        <v>139</v>
+      </c>
+      <c r="F50">
+        <v>18.2</v>
+      </c>
+      <c r="G50">
+        <v>123.2</v>
+      </c>
+      <c r="H50">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51">
+        <v>88.4</v>
+      </c>
+      <c r="E51">
+        <v>104.1</v>
+      </c>
+      <c r="F51">
+        <v>17.7</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52">
+        <v>92.3</v>
+      </c>
+      <c r="E52">
+        <v>107</v>
+      </c>
+      <c r="F52">
+        <v>15.9</v>
+      </c>
+      <c r="G52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53">
+        <v>129.2</v>
+      </c>
+      <c r="E53">
+        <v>148.7</v>
+      </c>
+      <c r="F53">
+        <v>15</v>
+      </c>
+      <c r="G53">
+        <v>123.2</v>
+      </c>
+      <c r="H53">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54">
+        <v>115.3</v>
+      </c>
+      <c r="E54">
+        <v>132.5</v>
+      </c>
+      <c r="F54">
+        <v>14.8</v>
+      </c>
+      <c r="G54">
+        <v>123.2</v>
+      </c>
+      <c r="H54">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55">
+        <v>126.9</v>
+      </c>
+      <c r="E55">
+        <v>144</v>
+      </c>
+      <c r="F55">
+        <v>13.5</v>
+      </c>
+      <c r="G55">
+        <v>123.2</v>
+      </c>
+      <c r="H55">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56">
+        <v>126.9</v>
+      </c>
+      <c r="E56">
+        <v>143</v>
+      </c>
+      <c r="F56">
+        <v>12.7</v>
+      </c>
+      <c r="G56">
+        <v>123.2</v>
+      </c>
+      <c r="H56">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57">
+        <v>92.3</v>
+      </c>
+      <c r="E57">
+        <v>103.9</v>
+      </c>
+      <c r="F57">
+        <v>12.5</v>
+      </c>
+      <c r="G57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58">
+        <v>100</v>
+      </c>
+      <c r="E58">
+        <v>112.3</v>
+      </c>
+      <c r="F58">
+        <v>12.3</v>
+      </c>
+      <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59">
+        <v>143.2</v>
+      </c>
+      <c r="E59">
+        <v>160.9</v>
+      </c>
+      <c r="F59">
+        <v>12.3</v>
+      </c>
+      <c r="G59">
+        <v>123.2</v>
+      </c>
+      <c r="H59">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60">
+        <v>105.5</v>
+      </c>
+      <c r="E60">
+        <v>118.4</v>
+      </c>
+      <c r="F60">
+        <v>12.2</v>
+      </c>
+      <c r="G60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" t="s">
+        <v>53</v>
+      </c>
+      <c r="D61">
+        <v>115.3</v>
+      </c>
+      <c r="E61">
+        <v>129</v>
+      </c>
+      <c r="F61">
+        <v>11.8</v>
+      </c>
+      <c r="G61">
+        <v>123.2</v>
+      </c>
+      <c r="H61">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62">
+        <v>98.2</v>
+      </c>
+      <c r="E62">
+        <v>109.8</v>
+      </c>
+      <c r="F62">
+        <v>11.7</v>
+      </c>
+      <c r="G62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63">
+        <v>96.1</v>
+      </c>
+      <c r="E63">
+        <v>106.9</v>
+      </c>
+      <c r="F63">
+        <v>11.2</v>
+      </c>
+      <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64">
+        <v>92.3</v>
+      </c>
+      <c r="E64">
+        <v>102.2</v>
+      </c>
+      <c r="F64">
+        <v>10.8</v>
+      </c>
+      <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65">
+        <v>103.8</v>
+      </c>
+      <c r="E65">
+        <v>114.5</v>
+      </c>
+      <c r="F65">
+        <v>10.3</v>
+      </c>
+      <c r="G65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66">
+        <v>73</v>
+      </c>
+      <c r="E66">
+        <v>80.5</v>
+      </c>
+      <c r="F66">
+        <v>10.1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67">
+        <v>155.8</v>
+      </c>
+      <c r="E67">
+        <v>170.1</v>
+      </c>
+      <c r="F67">
+        <v>9.1</v>
+      </c>
+      <c r="G67">
+        <v>123.2</v>
+      </c>
+      <c r="H67">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" t="s">
+        <v>56</v>
+      </c>
+      <c r="D68">
+        <v>135.2</v>
+      </c>
+      <c r="E68">
+        <v>146.6</v>
+      </c>
+      <c r="F68">
+        <v>8.4</v>
+      </c>
+      <c r="G68">
+        <v>123.2</v>
+      </c>
+      <c r="H68">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>66</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
+        <v>64</v>
+      </c>
+      <c r="D69">
+        <v>155.5</v>
+      </c>
+      <c r="E69">
+        <v>164.8</v>
+      </c>
+      <c r="F69">
+        <v>6</v>
+      </c>
+      <c r="G69">
+        <v>123.2</v>
+      </c>
+      <c r="H69">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>63</v>
+      </c>
+      <c r="D70">
+        <v>134.6</v>
+      </c>
+      <c r="E70">
+        <v>139.1</v>
+      </c>
+      <c r="F70">
+        <v>3.3</v>
+      </c>
+      <c r="G70">
+        <v>123.2</v>
+      </c>
+      <c r="H70">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>66</v>
+      </c>
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" t="s">
+        <v>65</v>
+      </c>
+      <c r="D71">
+        <v>146.1</v>
+      </c>
+      <c r="E71">
+        <v>136.6</v>
+      </c>
+      <c r="F71">
+        <v>-6.4</v>
+      </c>
+      <c r="G71">
+        <v>123.2</v>
+      </c>
+      <c r="H71">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72">
+        <v>88.4</v>
+      </c>
+      <c r="E72">
+        <v>156.3</v>
+      </c>
+      <c r="F72">
+        <v>76.7</v>
+      </c>
+      <c r="G72">
+        <v>123.1</v>
+      </c>
+      <c r="H72">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73">
+        <v>109</v>
+      </c>
+      <c r="E73">
+        <v>145.7</v>
+      </c>
+      <c r="F73">
+        <v>33.6</v>
+      </c>
+      <c r="G73">
+        <v>123.1</v>
+      </c>
+      <c r="H73">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74">
+        <v>100</v>
+      </c>
+      <c r="E74">
+        <v>131.8</v>
+      </c>
+      <c r="F74">
+        <v>31.8</v>
+      </c>
+      <c r="G74">
+        <v>123.1</v>
+      </c>
+      <c r="H74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75">
+        <v>80.7</v>
+      </c>
+      <c r="E75">
+        <v>104.3</v>
+      </c>
+      <c r="F75">
+        <v>29.1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76">
+        <v>81.8</v>
+      </c>
+      <c r="E76">
+        <v>100.1</v>
+      </c>
+      <c r="F76">
+        <v>22.3</v>
+      </c>
+      <c r="G76" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D77">
+        <v>167</v>
+      </c>
+      <c r="E77">
+        <v>203.9</v>
+      </c>
+      <c r="F77">
+        <v>22</v>
+      </c>
+      <c r="G77">
+        <v>123.1</v>
+      </c>
+      <c r="H77">
+        <v>65.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>70</v>
+      </c>
+      <c r="B78" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78">
+        <v>126.9</v>
+      </c>
+      <c r="E78">
+        <v>153.2</v>
+      </c>
+      <c r="F78">
+        <v>20.7</v>
+      </c>
+      <c r="G78">
+        <v>123.1</v>
+      </c>
+      <c r="H78">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>70</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79">
+        <v>116.9</v>
+      </c>
+      <c r="E79">
+        <v>138.3</v>
+      </c>
+      <c r="F79">
+        <v>18.2</v>
+      </c>
+      <c r="G79">
+        <v>123.1</v>
+      </c>
+      <c r="H79">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80">
+        <v>88.4</v>
+      </c>
+      <c r="E80">
+        <v>104.3</v>
+      </c>
+      <c r="F80">
+        <v>17.9</v>
+      </c>
+      <c r="G80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81">
+        <v>117.5</v>
+      </c>
+      <c r="E81">
+        <v>137.9</v>
+      </c>
+      <c r="F81">
+        <v>17.3</v>
+      </c>
+      <c r="G81">
+        <v>123.1</v>
+      </c>
+      <c r="H81">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82">
+        <v>92.3</v>
+      </c>
+      <c r="E82">
+        <v>108</v>
+      </c>
+      <c r="F82">
+        <v>17</v>
+      </c>
+      <c r="G82" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83">
+        <v>103.8</v>
+      </c>
+      <c r="E83">
+        <v>120.5</v>
+      </c>
+      <c r="F83">
+        <v>16</v>
+      </c>
+      <c r="G83" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84">
+        <v>92.3</v>
+      </c>
+      <c r="E84">
+        <v>106.6</v>
+      </c>
+      <c r="F84">
+        <v>15.5</v>
+      </c>
+      <c r="G84" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" t="s">
+        <v>45</v>
+      </c>
+      <c r="D85">
+        <v>92.3</v>
+      </c>
+      <c r="E85">
+        <v>106.5</v>
+      </c>
+      <c r="F85">
+        <v>15.4</v>
+      </c>
+      <c r="G85" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86" t="s">
+        <v>34</v>
+      </c>
+      <c r="C86" t="s">
+        <v>60</v>
+      </c>
+      <c r="D86">
+        <v>126.9</v>
+      </c>
+      <c r="E86">
+        <v>144.5</v>
+      </c>
+      <c r="F86">
+        <v>13.8</v>
+      </c>
+      <c r="G86">
+        <v>123.1</v>
+      </c>
+      <c r="H86">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>70</v>
+      </c>
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87">
+        <v>103.8</v>
+      </c>
+      <c r="E87">
+        <v>118</v>
+      </c>
+      <c r="F87">
+        <v>13.6</v>
+      </c>
+      <c r="G87" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88" t="s">
+        <v>49</v>
+      </c>
+      <c r="C88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D88">
+        <v>129.2</v>
+      </c>
+      <c r="E88">
+        <v>146.6</v>
+      </c>
+      <c r="F88">
+        <v>13.5</v>
+      </c>
+      <c r="G88">
+        <v>123.1</v>
+      </c>
+      <c r="H88">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>70</v>
+      </c>
+      <c r="B89" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89" t="s">
+        <v>62</v>
+      </c>
+      <c r="D89">
+        <v>143.2</v>
+      </c>
+      <c r="E89">
+        <v>162</v>
+      </c>
+      <c r="F89">
+        <v>13</v>
+      </c>
+      <c r="G89">
+        <v>123.1</v>
+      </c>
+      <c r="H89">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90" t="s">
+        <v>34</v>
+      </c>
+      <c r="C90" t="s">
+        <v>53</v>
+      </c>
+      <c r="D90">
+        <v>115.3</v>
+      </c>
+      <c r="E90">
+        <v>130.2</v>
+      </c>
+      <c r="F90">
+        <v>12.8</v>
+      </c>
+      <c r="G90">
+        <v>123.1</v>
+      </c>
+      <c r="H90">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91">
+        <v>98.2</v>
+      </c>
+      <c r="E91">
+        <v>110.2</v>
+      </c>
+      <c r="F91">
+        <v>12.1</v>
+      </c>
+      <c r="G91" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92" t="s">
+        <v>46</v>
+      </c>
+      <c r="D92">
+        <v>96.1</v>
+      </c>
+      <c r="E92">
+        <v>107.5</v>
+      </c>
+      <c r="F92">
+        <v>11.8</v>
+      </c>
+      <c r="G92" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93">
+        <v>115.3</v>
+      </c>
+      <c r="E93">
+        <v>128.3</v>
+      </c>
+      <c r="F93">
+        <v>11.2</v>
+      </c>
+      <c r="G93">
+        <v>123.1</v>
+      </c>
+      <c r="H93">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94" t="s">
+        <v>54</v>
+      </c>
+      <c r="C94" t="s">
+        <v>55</v>
+      </c>
+      <c r="D94">
+        <v>87.6</v>
+      </c>
+      <c r="E94">
+        <v>96.9</v>
+      </c>
+      <c r="F94">
+        <v>10.6</v>
+      </c>
+      <c r="G94" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95" t="s">
+        <v>58</v>
+      </c>
+      <c r="C95" t="s">
+        <v>59</v>
+      </c>
+      <c r="D95">
+        <v>155.8</v>
+      </c>
+      <c r="E95">
+        <v>172.4</v>
+      </c>
+      <c r="F95">
+        <v>10.6</v>
+      </c>
+      <c r="G95">
+        <v>123.1</v>
+      </c>
+      <c r="H95">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96">
+        <v>126.9</v>
+      </c>
+      <c r="E96">
+        <v>136.8</v>
+      </c>
+      <c r="F96">
+        <v>7.8</v>
+      </c>
+      <c r="G96">
+        <v>123.1</v>
+      </c>
+      <c r="H96">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" t="s">
+        <v>34</v>
+      </c>
+      <c r="C97" t="s">
+        <v>64</v>
+      </c>
+      <c r="D97">
+        <v>155.5</v>
+      </c>
+      <c r="E97">
+        <v>165.3</v>
+      </c>
+      <c r="F97">
+        <v>6.3</v>
+      </c>
+      <c r="G97">
+        <v>123.1</v>
+      </c>
+      <c r="H97">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98" t="s">
+        <v>41</v>
+      </c>
+      <c r="C98" t="s">
+        <v>56</v>
+      </c>
+      <c r="D98">
+        <v>135.2</v>
+      </c>
+      <c r="E98">
+        <v>139.9</v>
+      </c>
+      <c r="F98">
+        <v>3.4</v>
+      </c>
+      <c r="G98">
+        <v>123.1</v>
+      </c>
+      <c r="H98">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>70</v>
+      </c>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
+        <v>63</v>
+      </c>
+      <c r="D99">
+        <v>134.6</v>
+      </c>
+      <c r="E99">
+        <v>136.4</v>
+      </c>
+      <c r="F99">
+        <v>1.3</v>
+      </c>
+      <c r="G99">
+        <v>123.1</v>
+      </c>
+      <c r="H99">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" t="s">
+        <v>65</v>
+      </c>
+      <c r="D100">
+        <v>146.1</v>
+      </c>
+      <c r="E100">
+        <v>137.9</v>
+      </c>
+      <c r="F100">
+        <v>-5.6</v>
+      </c>
+      <c r="G100">
+        <v>123.1</v>
+      </c>
+      <c r="H100">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>71</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101">
+        <v>88.4</v>
+      </c>
+      <c r="E101">
+        <v>149.3</v>
+      </c>
+      <c r="F101">
+        <v>68.8</v>
+      </c>
+      <c r="G101">
+        <v>123.3</v>
+      </c>
+      <c r="H101">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>71</v>
+      </c>
+      <c r="B102" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102" t="s">
+        <v>35</v>
+      </c>
+      <c r="D102">
+        <v>100</v>
+      </c>
+      <c r="E102">
+        <v>135.7</v>
+      </c>
+      <c r="F102">
+        <v>35.7</v>
+      </c>
+      <c r="G102">
+        <v>123.3</v>
+      </c>
+      <c r="H102">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>71</v>
+      </c>
+      <c r="B103" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" t="s">
+        <v>32</v>
+      </c>
+      <c r="D103">
+        <v>109</v>
+      </c>
+      <c r="E103">
+        <v>144.4</v>
+      </c>
+      <c r="F103">
+        <v>32.4</v>
+      </c>
+      <c r="G103">
+        <v>123.3</v>
+      </c>
+      <c r="H103">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>71</v>
+      </c>
+      <c r="B104" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104">
+        <v>80.7</v>
+      </c>
+      <c r="E104">
+        <v>104</v>
+      </c>
+      <c r="F104">
+        <v>28.8</v>
+      </c>
+      <c r="G104" t="s">
+        <v>16</v>
+      </c>
+      <c r="H104" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>71</v>
+      </c>
+      <c r="B105" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105">
+        <v>167</v>
+      </c>
+      <c r="E105">
+        <v>205.2</v>
+      </c>
+      <c r="F105">
+        <v>22.8</v>
+      </c>
+      <c r="G105">
+        <v>123.3</v>
+      </c>
+      <c r="H105">
+        <v>66.4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>71</v>
+      </c>
+      <c r="B106" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106">
+        <v>81.8</v>
+      </c>
+      <c r="E106">
+        <v>98.7</v>
+      </c>
+      <c r="F106">
+        <v>20.6</v>
+      </c>
+      <c r="G106" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>71</v>
+      </c>
+      <c r="B107" t="s">
+        <v>41</v>
+      </c>
+      <c r="C107" t="s">
+        <v>42</v>
+      </c>
+      <c r="D107">
+        <v>126.9</v>
+      </c>
+      <c r="E107">
+        <v>152</v>
+      </c>
+      <c r="F107">
+        <v>19.7</v>
+      </c>
+      <c r="G107">
+        <v>123.3</v>
+      </c>
+      <c r="H107">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>71</v>
+      </c>
+      <c r="B108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C108" t="s">
+        <v>47</v>
+      </c>
+      <c r="D108">
+        <v>88.4</v>
+      </c>
+      <c r="E108">
+        <v>103.9</v>
+      </c>
+      <c r="F108">
+        <v>17.4</v>
+      </c>
+      <c r="G108" t="s">
+        <v>16</v>
+      </c>
+      <c r="H108" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>71</v>
+      </c>
+      <c r="B109" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109">
+        <v>116.9</v>
+      </c>
+      <c r="E109">
+        <v>136.6</v>
+      </c>
+      <c r="F109">
+        <v>16.8</v>
+      </c>
+      <c r="G109">
+        <v>123.3</v>
+      </c>
+      <c r="H109">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>71</v>
+      </c>
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" t="s">
+        <v>69</v>
+      </c>
+      <c r="D110">
+        <v>103.8</v>
+      </c>
+      <c r="E110">
+        <v>120.4</v>
+      </c>
+      <c r="F110">
+        <v>16</v>
+      </c>
+      <c r="G110" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>71</v>
+      </c>
+      <c r="B111" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" t="s">
+        <v>60</v>
+      </c>
+      <c r="D111">
+        <v>126.9</v>
+      </c>
+      <c r="E111">
+        <v>147.1</v>
+      </c>
+      <c r="F111">
+        <v>15.9</v>
+      </c>
+      <c r="G111">
+        <v>123.3</v>
+      </c>
+      <c r="H111">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>71</v>
+      </c>
+      <c r="B112" t="s">
+        <v>19</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112">
+        <v>92.3</v>
+      </c>
+      <c r="E112">
+        <v>106.5</v>
+      </c>
+      <c r="F112">
+        <v>15.4</v>
+      </c>
+      <c r="G112" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>71</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" t="s">
+        <v>30</v>
+      </c>
+      <c r="D113">
+        <v>117.5</v>
+      </c>
+      <c r="E113">
+        <v>135.7</v>
+      </c>
+      <c r="F113">
+        <v>15.4</v>
+      </c>
+      <c r="G113">
+        <v>123.3</v>
+      </c>
+      <c r="H113">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>71</v>
+      </c>
+      <c r="B114" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114">
+        <v>92.3</v>
+      </c>
+      <c r="E114">
+        <v>105.7</v>
+      </c>
+      <c r="F114">
+        <v>14.5</v>
+      </c>
+      <c r="G114" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>71</v>
+      </c>
+      <c r="B115" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" t="s">
+        <v>24</v>
+      </c>
+      <c r="D115">
+        <v>103.8</v>
+      </c>
+      <c r="E115">
+        <v>118.8</v>
+      </c>
+      <c r="F115">
+        <v>14.4</v>
+      </c>
+      <c r="G115" t="s">
+        <v>16</v>
+      </c>
+      <c r="H115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>71</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>45</v>
+      </c>
+      <c r="D116">
+        <v>92.3</v>
+      </c>
+      <c r="E116">
+        <v>105.5</v>
+      </c>
+      <c r="F116">
+        <v>14.3</v>
+      </c>
+      <c r="G116" t="s">
+        <v>16</v>
+      </c>
+      <c r="H116" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>71</v>
+      </c>
+      <c r="B117" t="s">
+        <v>34</v>
+      </c>
+      <c r="C117" t="s">
+        <v>53</v>
+      </c>
+      <c r="D117">
+        <v>115.3</v>
+      </c>
+      <c r="E117">
+        <v>130.9</v>
+      </c>
+      <c r="F117">
+        <v>13.5</v>
+      </c>
+      <c r="G117">
+        <v>123.3</v>
+      </c>
+      <c r="H117">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>71</v>
+      </c>
+      <c r="B118" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" t="s">
+        <v>46</v>
+      </c>
+      <c r="D118">
+        <v>96.1</v>
+      </c>
+      <c r="E118">
+        <v>107.5</v>
+      </c>
+      <c r="F118">
+        <v>11.8</v>
+      </c>
+      <c r="G118" t="s">
+        <v>16</v>
+      </c>
+      <c r="H118" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>71</v>
+      </c>
+      <c r="B119" t="s">
+        <v>58</v>
+      </c>
+      <c r="C119" t="s">
+        <v>59</v>
+      </c>
+      <c r="D119">
+        <v>155.8</v>
+      </c>
+      <c r="E119">
+        <v>173.7</v>
+      </c>
+      <c r="F119">
+        <v>11.5</v>
+      </c>
+      <c r="G119">
+        <v>123.3</v>
+      </c>
+      <c r="H119">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>71</v>
+      </c>
+      <c r="B120" t="s">
+        <v>27</v>
+      </c>
+      <c r="C120" t="s">
+        <v>28</v>
+      </c>
+      <c r="D120">
+        <v>115.3</v>
+      </c>
+      <c r="E120">
+        <v>128.6</v>
+      </c>
+      <c r="F120">
+        <v>11.4</v>
+      </c>
+      <c r="G120">
+        <v>123.3</v>
+      </c>
+      <c r="H120">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>71</v>
+      </c>
+      <c r="B121" t="s">
+        <v>41</v>
+      </c>
+      <c r="C121" t="s">
+        <v>62</v>
+      </c>
+      <c r="D121">
+        <v>143.2</v>
+      </c>
+      <c r="E121">
+        <v>159.4</v>
+      </c>
+      <c r="F121">
+        <v>11.3</v>
+      </c>
+      <c r="G121">
+        <v>123.3</v>
+      </c>
+      <c r="H121">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>71</v>
+      </c>
+      <c r="B122" t="s">
+        <v>54</v>
+      </c>
+      <c r="C122" t="s">
+        <v>55</v>
+      </c>
+      <c r="D122">
+        <v>87.6</v>
+      </c>
+      <c r="E122">
+        <v>97.4</v>
+      </c>
+      <c r="F122">
+        <v>11.2</v>
+      </c>
+      <c r="G122" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>71</v>
+      </c>
+      <c r="B123" t="s">
+        <v>72</v>
+      </c>
+      <c r="C123" t="s">
+        <v>73</v>
+      </c>
+      <c r="D123">
+        <v>123.5</v>
+      </c>
+      <c r="E123">
+        <v>136</v>
+      </c>
+      <c r="F123">
+        <v>10.1</v>
+      </c>
+      <c r="G123">
+        <v>123.3</v>
+      </c>
+      <c r="H123">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>71</v>
+      </c>
+      <c r="B124" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" t="s">
+        <v>64</v>
+      </c>
+      <c r="D124">
+        <v>155.5</v>
+      </c>
+      <c r="E124">
+        <v>165.3</v>
+      </c>
+      <c r="F124">
+        <v>6.3</v>
+      </c>
+      <c r="G124">
+        <v>123.3</v>
+      </c>
+      <c r="H124">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>71</v>
+      </c>
+      <c r="B125" t="s">
+        <v>49</v>
+      </c>
+      <c r="C125" t="s">
+        <v>50</v>
+      </c>
+      <c r="D125">
+        <v>138.4</v>
+      </c>
+      <c r="E125">
+        <v>145.5</v>
+      </c>
+      <c r="F125">
+        <v>5.1</v>
+      </c>
+      <c r="G125">
+        <v>123.3</v>
+      </c>
+      <c r="H125">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" t="s">
+        <v>56</v>
+      </c>
+      <c r="D126">
+        <v>135.2</v>
+      </c>
+      <c r="E126">
+        <v>140.2</v>
+      </c>
+      <c r="F126">
+        <v>3.6</v>
+      </c>
+      <c r="G126">
+        <v>123.3</v>
+      </c>
+      <c r="H126">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>71</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" t="s">
+        <v>63</v>
+      </c>
+      <c r="D127">
+        <v>134.6</v>
+      </c>
+      <c r="E127">
+        <v>138</v>
+      </c>
+      <c r="F127">
+        <v>2.5</v>
+      </c>
+      <c r="G127">
+        <v>123.3</v>
+      </c>
+      <c r="H127">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>74</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128">
+        <v>88.4</v>
+      </c>
+      <c r="E128">
+        <v>151.6</v>
+      </c>
+      <c r="F128">
+        <v>71.4</v>
+      </c>
+      <c r="G128">
+        <v>122.7</v>
+      </c>
+      <c r="H128">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>74</v>
+      </c>
+      <c r="B129" t="s">
+        <v>34</v>
+      </c>
+      <c r="C129" t="s">
+        <v>35</v>
+      </c>
+      <c r="D129">
+        <v>100</v>
+      </c>
+      <c r="E129">
+        <v>133.2</v>
+      </c>
+      <c r="F129">
+        <v>33.2</v>
+      </c>
+      <c r="G129">
+        <v>122.7</v>
+      </c>
+      <c r="H129">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>74</v>
+      </c>
+      <c r="B130" t="s">
+        <v>31</v>
+      </c>
+      <c r="C130" t="s">
+        <v>32</v>
+      </c>
+      <c r="D130">
+        <v>109</v>
+      </c>
+      <c r="E130">
+        <v>144.2</v>
+      </c>
+      <c r="F130">
+        <v>32.3</v>
+      </c>
+      <c r="G130">
+        <v>122.7</v>
+      </c>
+      <c r="H130">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>74</v>
+      </c>
+      <c r="B131" t="s">
+        <v>9</v>
+      </c>
+      <c r="C131" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131">
+        <v>80.7</v>
+      </c>
+      <c r="E131">
+        <v>103.8</v>
+      </c>
+      <c r="F131">
+        <v>28.5</v>
+      </c>
+      <c r="G131" t="s">
+        <v>16</v>
+      </c>
+      <c r="H131" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>74</v>
+      </c>
+      <c r="B132" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" t="s">
+        <v>52</v>
+      </c>
+      <c r="D132">
+        <v>167</v>
+      </c>
+      <c r="E132">
+        <v>212.8</v>
+      </c>
+      <c r="F132">
+        <v>27.4</v>
+      </c>
+      <c r="G132">
+        <v>122.7</v>
+      </c>
+      <c r="H132">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>74</v>
+      </c>
+      <c r="B133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133">
+        <v>92.3</v>
+      </c>
+      <c r="E133">
+        <v>107.9</v>
+      </c>
+      <c r="F133">
+        <v>16.9</v>
+      </c>
+      <c r="G133" t="s">
+        <v>16</v>
+      </c>
+      <c r="H133" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>74</v>
+      </c>
+      <c r="B134" t="s">
+        <v>43</v>
+      </c>
+      <c r="C134" t="s">
+        <v>47</v>
+      </c>
+      <c r="D134">
+        <v>88.4</v>
+      </c>
+      <c r="E134">
+        <v>103.2</v>
+      </c>
+      <c r="F134">
+        <v>16.7</v>
+      </c>
+      <c r="G134" t="s">
+        <v>16</v>
+      </c>
+      <c r="H134" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>74</v>
+      </c>
+      <c r="B135" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" t="s">
+        <v>15</v>
+      </c>
+      <c r="D135">
+        <v>81.8</v>
+      </c>
+      <c r="E135">
+        <v>95.4</v>
+      </c>
+      <c r="F135">
+        <v>16.6</v>
+      </c>
+      <c r="G135" t="s">
+        <v>16</v>
+      </c>
+      <c r="H135" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>74</v>
+      </c>
+      <c r="B136" t="s">
+        <v>27</v>
+      </c>
+      <c r="C136" t="s">
+        <v>69</v>
+      </c>
+      <c r="D136">
+        <v>103.8</v>
+      </c>
+      <c r="E136">
+        <v>119.8</v>
+      </c>
+      <c r="F136">
+        <v>15.3</v>
+      </c>
+      <c r="G136" t="s">
+        <v>16</v>
+      </c>
+      <c r="H136" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>74</v>
+      </c>
+      <c r="B137" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137" t="s">
+        <v>26</v>
+      </c>
+      <c r="D137">
+        <v>116.9</v>
+      </c>
+      <c r="E137">
+        <v>134.3</v>
+      </c>
+      <c r="F137">
+        <v>14.8</v>
+      </c>
+      <c r="G137">
+        <v>122.7</v>
+      </c>
+      <c r="H137">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>74</v>
+      </c>
+      <c r="B138" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138">
+        <v>126.9</v>
+      </c>
+      <c r="E138">
+        <v>145.6</v>
+      </c>
+      <c r="F138">
+        <v>14.7</v>
+      </c>
+      <c r="G138">
+        <v>122.7</v>
+      </c>
+      <c r="H138">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>74</v>
+      </c>
+      <c r="B139" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139" t="s">
+        <v>60</v>
+      </c>
+      <c r="D139">
+        <v>126.9</v>
+      </c>
+      <c r="E139">
+        <v>145.5</v>
+      </c>
+      <c r="F139">
+        <v>14.6</v>
+      </c>
+      <c r="G139">
+        <v>122.7</v>
+      </c>
+      <c r="H139">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>74</v>
+      </c>
+      <c r="B140" t="s">
+        <v>27</v>
+      </c>
+      <c r="C140" t="s">
+        <v>67</v>
+      </c>
+      <c r="D140">
+        <v>100</v>
+      </c>
+      <c r="E140">
+        <v>113.5</v>
+      </c>
+      <c r="F140">
+        <v>13.5</v>
+      </c>
+      <c r="G140" t="s">
+        <v>16</v>
+      </c>
+      <c r="H140" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>74</v>
+      </c>
+      <c r="B141" t="s">
+        <v>34</v>
+      </c>
+      <c r="C141" t="s">
+        <v>53</v>
+      </c>
+      <c r="D141">
+        <v>115.3</v>
+      </c>
+      <c r="E141">
+        <v>130.8</v>
+      </c>
+      <c r="F141">
+        <v>13.4</v>
+      </c>
+      <c r="G141">
+        <v>122.7</v>
+      </c>
+      <c r="H141">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>74</v>
+      </c>
+      <c r="B142" t="s">
+        <v>23</v>
+      </c>
+      <c r="C142" t="s">
+        <v>24</v>
+      </c>
+      <c r="D142">
+        <v>103.8</v>
+      </c>
+      <c r="E142">
+        <v>117.2</v>
+      </c>
+      <c r="F142">
+        <v>12.9</v>
+      </c>
+      <c r="G142" t="s">
+        <v>16</v>
+      </c>
+      <c r="H142" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>74</v>
+      </c>
+      <c r="B143" t="s">
+        <v>58</v>
+      </c>
+      <c r="C143" t="s">
+        <v>59</v>
+      </c>
+      <c r="D143">
+        <v>155.8</v>
+      </c>
+      <c r="E143">
+        <v>175.6</v>
+      </c>
+      <c r="F143">
+        <v>12.7</v>
+      </c>
+      <c r="G143">
+        <v>122.7</v>
+      </c>
+      <c r="H143">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>74</v>
+      </c>
+      <c r="B144" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144" t="s">
+        <v>46</v>
+      </c>
+      <c r="D144">
+        <v>96.1</v>
+      </c>
+      <c r="E144">
+        <v>108</v>
+      </c>
+      <c r="F144">
+        <v>12.4</v>
+      </c>
+      <c r="G144" t="s">
+        <v>16</v>
+      </c>
+      <c r="H144" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>74</v>
+      </c>
+      <c r="B145" t="s">
+        <v>72</v>
+      </c>
+      <c r="C145" t="s">
+        <v>73</v>
+      </c>
+      <c r="D145">
+        <v>123.5</v>
+      </c>
+      <c r="E145">
+        <v>138.7</v>
+      </c>
+      <c r="F145">
+        <v>12.2</v>
+      </c>
+      <c r="G145">
+        <v>122.7</v>
+      </c>
+      <c r="H145">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>74</v>
+      </c>
+      <c r="B146" t="s">
+        <v>29</v>
+      </c>
+      <c r="C146" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146">
+        <v>117.5</v>
+      </c>
+      <c r="E146">
+        <v>131.8</v>
+      </c>
+      <c r="F146">
+        <v>12.1</v>
+      </c>
+      <c r="G146">
+        <v>122.7</v>
+      </c>
+      <c r="H146">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>74</v>
+      </c>
+      <c r="B147" t="s">
+        <v>75</v>
+      </c>
+      <c r="C147" t="s">
+        <v>76</v>
+      </c>
+      <c r="D147">
+        <v>119.8</v>
+      </c>
+      <c r="E147">
+        <v>134.2</v>
+      </c>
+      <c r="F147">
+        <v>12</v>
+      </c>
+      <c r="G147">
+        <v>122.7</v>
+      </c>
+      <c r="H147">
+        <v>9.3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>74</v>
+      </c>
+      <c r="B148" t="s">
+        <v>14</v>
+      </c>
+      <c r="C148" t="s">
+        <v>45</v>
+      </c>
+      <c r="D148">
+        <v>92.3</v>
+      </c>
+      <c r="E148">
+        <v>103.4</v>
+      </c>
+      <c r="F148">
+        <v>12</v>
+      </c>
+      <c r="G148" t="s">
+        <v>16</v>
+      </c>
+      <c r="H148" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>74</v>
+      </c>
+      <c r="B149" t="s">
+        <v>54</v>
+      </c>
+      <c r="C149" t="s">
+        <v>55</v>
+      </c>
+      <c r="D149">
+        <v>87.6</v>
+      </c>
+      <c r="E149">
+        <v>97.7</v>
+      </c>
+      <c r="F149">
+        <v>11.5</v>
+      </c>
+      <c r="G149" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>74</v>
+      </c>
+      <c r="B150" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150">
+        <v>92.3</v>
+      </c>
+      <c r="E150">
+        <v>102.8</v>
+      </c>
+      <c r="F150">
+        <v>11.4</v>
+      </c>
+      <c r="G150" t="s">
+        <v>16</v>
+      </c>
+      <c r="H150" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>74</v>
+      </c>
+      <c r="B151" t="s">
+        <v>41</v>
+      </c>
+      <c r="C151" t="s">
+        <v>62</v>
+      </c>
+      <c r="D151">
+        <v>143.2</v>
+      </c>
+      <c r="E151">
+        <v>157.5</v>
+      </c>
+      <c r="F151">
+        <v>9.9</v>
+      </c>
+      <c r="G151">
+        <v>122.7</v>
+      </c>
+      <c r="H151">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>74</v>
+      </c>
+      <c r="B152" t="s">
+        <v>77</v>
+      </c>
+      <c r="C152" t="s">
+        <v>78</v>
+      </c>
+      <c r="D152">
+        <v>123</v>
+      </c>
+      <c r="E152">
+        <v>135</v>
+      </c>
+      <c r="F152">
+        <v>9.7</v>
+      </c>
+      <c r="G152">
+        <v>122.7</v>
+      </c>
+      <c r="H152">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>74</v>
+      </c>
+      <c r="B153" t="s">
+        <v>34</v>
+      </c>
+      <c r="C153" t="s">
+        <v>64</v>
+      </c>
+      <c r="D153">
+        <v>155.5</v>
+      </c>
+      <c r="E153">
+        <v>163.8</v>
+      </c>
+      <c r="F153">
+        <v>5.3</v>
+      </c>
+      <c r="G153">
+        <v>122.7</v>
+      </c>
+      <c r="H153">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>74</v>
+      </c>
+      <c r="B154" t="s">
+        <v>49</v>
+      </c>
+      <c r="C154" t="s">
+        <v>50</v>
+      </c>
+      <c r="D154">
+        <v>138.4</v>
+      </c>
+      <c r="E154">
+        <v>145.3</v>
+      </c>
+      <c r="F154">
+        <v>4.9</v>
+      </c>
+      <c r="G154">
+        <v>122.7</v>
+      </c>
+      <c r="H154">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>74</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>63</v>
+      </c>
+      <c r="D155">
+        <v>134.6</v>
+      </c>
+      <c r="E155">
+        <v>139.9</v>
+      </c>
+      <c r="F155">
+        <v>3.9</v>
+      </c>
+      <c r="G155">
+        <v>122.7</v>
+      </c>
+      <c r="H155">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>74</v>
+      </c>
+      <c r="B156" t="s">
+        <v>41</v>
+      </c>
+      <c r="C156" t="s">
+        <v>56</v>
+      </c>
+      <c r="D156">
+        <v>135.2</v>
+      </c>
+      <c r="E156">
+        <v>137.9</v>
+      </c>
+      <c r="F156">
+        <v>2</v>
+      </c>
+      <c r="G156">
+        <v>122.7</v>
+      </c>
+      <c r="H156">
+        <v>12.4</v>
       </c>
     </row>
   </sheetData>

--- a/source/8、绩效异常岗位/3、倒包岗/倒包岗-6月.xlsx
+++ b/source/8、绩效异常岗位/3、倒包岗/倒包岗-6月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="91">
   <si>
     <t>岗位类型</t>
   </si>
@@ -281,6 +281,27 @@
   </si>
   <si>
     <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>南通</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1232,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I240"/>
+  <dimension ref="A1:I368"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8172,6 +8193,3718 @@
       </c>
       <c r="I240">
         <v>12.6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" t="s">
+        <v>9</v>
+      </c>
+      <c r="B241" t="s">
+        <v>84</v>
+      </c>
+      <c r="C241" t="s">
+        <v>13</v>
+      </c>
+      <c r="D241" t="s">
+        <v>14</v>
+      </c>
+      <c r="E241">
+        <v>88.4</v>
+      </c>
+      <c r="F241">
+        <v>144.6</v>
+      </c>
+      <c r="G241">
+        <v>63.5</v>
+      </c>
+      <c r="H241">
+        <v>120.6</v>
+      </c>
+      <c r="I241">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" t="s">
+        <v>9</v>
+      </c>
+      <c r="B242" t="s">
+        <v>84</v>
+      </c>
+      <c r="C242" t="s">
+        <v>36</v>
+      </c>
+      <c r="D242" t="s">
+        <v>37</v>
+      </c>
+      <c r="E242">
+        <v>100</v>
+      </c>
+      <c r="F242">
+        <v>131.2</v>
+      </c>
+      <c r="G242">
+        <v>31.2</v>
+      </c>
+      <c r="H242">
+        <v>120.6</v>
+      </c>
+      <c r="I242">
+        <v>8.7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" t="s">
+        <v>9</v>
+      </c>
+      <c r="B243" t="s">
+        <v>84</v>
+      </c>
+      <c r="C243" t="s">
+        <v>33</v>
+      </c>
+      <c r="D243" t="s">
+        <v>34</v>
+      </c>
+      <c r="E243">
+        <v>109</v>
+      </c>
+      <c r="F243">
+        <v>134.8</v>
+      </c>
+      <c r="G243">
+        <v>23.6</v>
+      </c>
+      <c r="H243">
+        <v>120.6</v>
+      </c>
+      <c r="I243">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" t="s">
+        <v>9</v>
+      </c>
+      <c r="B244" t="s">
+        <v>84</v>
+      </c>
+      <c r="C244" t="s">
+        <v>11</v>
+      </c>
+      <c r="D244" t="s">
+        <v>12</v>
+      </c>
+      <c r="E244">
+        <v>80.7</v>
+      </c>
+      <c r="F244">
+        <v>98.9</v>
+      </c>
+      <c r="G244">
+        <v>22.5</v>
+      </c>
+      <c r="H244" t="s">
+        <v>18</v>
+      </c>
+      <c r="I244" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" t="s">
+        <v>9</v>
+      </c>
+      <c r="B245" t="s">
+        <v>84</v>
+      </c>
+      <c r="C245" t="s">
+        <v>33</v>
+      </c>
+      <c r="D245" t="s">
+        <v>54</v>
+      </c>
+      <c r="E245">
+        <v>167</v>
+      </c>
+      <c r="F245">
+        <v>204.7</v>
+      </c>
+      <c r="G245">
+        <v>22.5</v>
+      </c>
+      <c r="H245">
+        <v>120.6</v>
+      </c>
+      <c r="I245">
+        <v>69.6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" t="s">
+        <v>9</v>
+      </c>
+      <c r="B246" t="s">
+        <v>84</v>
+      </c>
+      <c r="C246" t="s">
+        <v>21</v>
+      </c>
+      <c r="D246" t="s">
+        <v>70</v>
+      </c>
+      <c r="E246">
+        <v>92.3</v>
+      </c>
+      <c r="F246">
+        <v>109</v>
+      </c>
+      <c r="G246">
+        <v>18.1</v>
+      </c>
+      <c r="H246" t="s">
+        <v>18</v>
+      </c>
+      <c r="I246" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" t="s">
+        <v>84</v>
+      </c>
+      <c r="C247" t="s">
+        <v>45</v>
+      </c>
+      <c r="D247" t="s">
+        <v>49</v>
+      </c>
+      <c r="E247">
+        <v>88.4</v>
+      </c>
+      <c r="F247">
+        <v>101.3</v>
+      </c>
+      <c r="G247">
+        <v>14.5</v>
+      </c>
+      <c r="H247" t="s">
+        <v>18</v>
+      </c>
+      <c r="I247" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" t="s">
+        <v>9</v>
+      </c>
+      <c r="B248" t="s">
+        <v>84</v>
+      </c>
+      <c r="C248" t="s">
+        <v>29</v>
+      </c>
+      <c r="D248" t="s">
+        <v>71</v>
+      </c>
+      <c r="E248">
+        <v>103.8</v>
+      </c>
+      <c r="F248">
+        <v>118.7</v>
+      </c>
+      <c r="G248">
+        <v>14.3</v>
+      </c>
+      <c r="H248" t="s">
+        <v>18</v>
+      </c>
+      <c r="I248" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" t="s">
+        <v>9</v>
+      </c>
+      <c r="B249" t="s">
+        <v>84</v>
+      </c>
+      <c r="C249" t="s">
+        <v>29</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249">
+        <v>100</v>
+      </c>
+      <c r="F249">
+        <v>113.9</v>
+      </c>
+      <c r="G249">
+        <v>13.9</v>
+      </c>
+      <c r="H249" t="s">
+        <v>18</v>
+      </c>
+      <c r="I249" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" t="s">
+        <v>9</v>
+      </c>
+      <c r="B250" t="s">
+        <v>84</v>
+      </c>
+      <c r="C250" t="s">
+        <v>36</v>
+      </c>
+      <c r="D250" t="s">
+        <v>55</v>
+      </c>
+      <c r="E250">
+        <v>115.3</v>
+      </c>
+      <c r="F250">
+        <v>130.3</v>
+      </c>
+      <c r="G250">
+        <v>12.9</v>
+      </c>
+      <c r="H250">
+        <v>120.6</v>
+      </c>
+      <c r="I250">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B251" t="s">
+        <v>84</v>
+      </c>
+      <c r="C251" t="s">
+        <v>60</v>
+      </c>
+      <c r="D251" t="s">
+        <v>61</v>
+      </c>
+      <c r="E251">
+        <v>155.8</v>
+      </c>
+      <c r="F251">
+        <v>174.4</v>
+      </c>
+      <c r="G251">
+        <v>11.9</v>
+      </c>
+      <c r="H251">
+        <v>120.6</v>
+      </c>
+      <c r="I251">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B252" t="s">
+        <v>84</v>
+      </c>
+      <c r="C252" t="s">
+        <v>77</v>
+      </c>
+      <c r="D252" t="s">
+        <v>78</v>
+      </c>
+      <c r="E252">
+        <v>119.8</v>
+      </c>
+      <c r="F252">
+        <v>133.7</v>
+      </c>
+      <c r="G252">
+        <v>11.6</v>
+      </c>
+      <c r="H252">
+        <v>120.6</v>
+      </c>
+      <c r="I252">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B253" t="s">
+        <v>84</v>
+      </c>
+      <c r="C253" t="s">
+        <v>27</v>
+      </c>
+      <c r="D253" t="s">
+        <v>28</v>
+      </c>
+      <c r="E253">
+        <v>116.9</v>
+      </c>
+      <c r="F253">
+        <v>130.1</v>
+      </c>
+      <c r="G253">
+        <v>11.2</v>
+      </c>
+      <c r="H253">
+        <v>120.6</v>
+      </c>
+      <c r="I253">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" t="s">
+        <v>9</v>
+      </c>
+      <c r="B254" t="s">
+        <v>84</v>
+      </c>
+      <c r="C254" t="s">
+        <v>36</v>
+      </c>
+      <c r="D254" t="s">
+        <v>62</v>
+      </c>
+      <c r="E254">
+        <v>126.9</v>
+      </c>
+      <c r="F254">
+        <v>140.9</v>
+      </c>
+      <c r="G254">
+        <v>11</v>
+      </c>
+      <c r="H254">
+        <v>120.6</v>
+      </c>
+      <c r="I254">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B255" t="s">
+        <v>84</v>
+      </c>
+      <c r="C255" t="s">
+        <v>11</v>
+      </c>
+      <c r="D255" t="s">
+        <v>53</v>
+      </c>
+      <c r="E255">
+        <v>92.3</v>
+      </c>
+      <c r="F255">
+        <v>102.2</v>
+      </c>
+      <c r="G255">
+        <v>10.7</v>
+      </c>
+      <c r="H255" t="s">
+        <v>18</v>
+      </c>
+      <c r="I255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256" t="s">
+        <v>84</v>
+      </c>
+      <c r="C256" t="s">
+        <v>79</v>
+      </c>
+      <c r="D256" t="s">
+        <v>80</v>
+      </c>
+      <c r="E256">
+        <v>123</v>
+      </c>
+      <c r="F256">
+        <v>136.1</v>
+      </c>
+      <c r="G256">
+        <v>10.5</v>
+      </c>
+      <c r="H256">
+        <v>120.6</v>
+      </c>
+      <c r="I256">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B257" t="s">
+        <v>84</v>
+      </c>
+      <c r="C257" t="s">
+        <v>56</v>
+      </c>
+      <c r="D257" t="s">
+        <v>57</v>
+      </c>
+      <c r="E257">
+        <v>87.6</v>
+      </c>
+      <c r="F257">
+        <v>96.5</v>
+      </c>
+      <c r="G257">
+        <v>10</v>
+      </c>
+      <c r="H257" t="s">
+        <v>18</v>
+      </c>
+      <c r="I257" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B258" t="s">
+        <v>84</v>
+      </c>
+      <c r="C258" t="s">
+        <v>74</v>
+      </c>
+      <c r="D258" t="s">
+        <v>75</v>
+      </c>
+      <c r="E258">
+        <v>126.9</v>
+      </c>
+      <c r="F258">
+        <v>139</v>
+      </c>
+      <c r="G258">
+        <v>9.5</v>
+      </c>
+      <c r="H258">
+        <v>120.6</v>
+      </c>
+      <c r="I258">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" t="s">
+        <v>84</v>
+      </c>
+      <c r="C259" t="s">
+        <v>43</v>
+      </c>
+      <c r="D259" t="s">
+        <v>44</v>
+      </c>
+      <c r="E259">
+        <v>126.9</v>
+      </c>
+      <c r="F259">
+        <v>137.8</v>
+      </c>
+      <c r="G259">
+        <v>8.5</v>
+      </c>
+      <c r="H259">
+        <v>120.6</v>
+      </c>
+      <c r="I259">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B260" t="s">
+        <v>84</v>
+      </c>
+      <c r="C260" t="s">
+        <v>43</v>
+      </c>
+      <c r="D260" t="s">
+        <v>64</v>
+      </c>
+      <c r="E260">
+        <v>143.2</v>
+      </c>
+      <c r="F260">
+        <v>151</v>
+      </c>
+      <c r="G260">
+        <v>5.4</v>
+      </c>
+      <c r="H260">
+        <v>120.6</v>
+      </c>
+      <c r="I260">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B261" t="s">
+        <v>84</v>
+      </c>
+      <c r="C261" t="s">
+        <v>21</v>
+      </c>
+      <c r="D261" t="s">
+        <v>22</v>
+      </c>
+      <c r="E261">
+        <v>126.9</v>
+      </c>
+      <c r="F261">
+        <v>133.1</v>
+      </c>
+      <c r="G261">
+        <v>4.9</v>
+      </c>
+      <c r="H261">
+        <v>120.6</v>
+      </c>
+      <c r="I261">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" t="s">
+        <v>9</v>
+      </c>
+      <c r="B262" t="s">
+        <v>84</v>
+      </c>
+      <c r="C262" t="s">
+        <v>36</v>
+      </c>
+      <c r="D262" t="s">
+        <v>66</v>
+      </c>
+      <c r="E262">
+        <v>155.5</v>
+      </c>
+      <c r="F262">
+        <v>161.7</v>
+      </c>
+      <c r="G262">
+        <v>4</v>
+      </c>
+      <c r="H262">
+        <v>120.6</v>
+      </c>
+      <c r="I262">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" t="s">
+        <v>9</v>
+      </c>
+      <c r="B263" t="s">
+        <v>84</v>
+      </c>
+      <c r="C263" t="s">
+        <v>51</v>
+      </c>
+      <c r="D263" t="s">
+        <v>52</v>
+      </c>
+      <c r="E263">
+        <v>138.4</v>
+      </c>
+      <c r="F263">
+        <v>143.2</v>
+      </c>
+      <c r="G263">
+        <v>3.4</v>
+      </c>
+      <c r="H263">
+        <v>120.6</v>
+      </c>
+      <c r="I263">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" t="s">
+        <v>9</v>
+      </c>
+      <c r="B264" t="s">
+        <v>84</v>
+      </c>
+      <c r="C264" t="s">
+        <v>13</v>
+      </c>
+      <c r="D264" t="s">
+        <v>65</v>
+      </c>
+      <c r="E264">
+        <v>134.6</v>
+      </c>
+      <c r="F264">
+        <v>137.6</v>
+      </c>
+      <c r="G264">
+        <v>2.2</v>
+      </c>
+      <c r="H264">
+        <v>120.6</v>
+      </c>
+      <c r="I264">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" t="s">
+        <v>9</v>
+      </c>
+      <c r="B265" t="s">
+        <v>84</v>
+      </c>
+      <c r="C265" t="s">
+        <v>43</v>
+      </c>
+      <c r="D265" t="s">
+        <v>58</v>
+      </c>
+      <c r="E265">
+        <v>135.2</v>
+      </c>
+      <c r="F265">
+        <v>135.2</v>
+      </c>
+      <c r="G265">
+        <v>0</v>
+      </c>
+      <c r="H265">
+        <v>120.6</v>
+      </c>
+      <c r="I265">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" t="s">
+        <v>9</v>
+      </c>
+      <c r="B266" t="s">
+        <v>85</v>
+      </c>
+      <c r="C266" t="s">
+        <v>13</v>
+      </c>
+      <c r="D266" t="s">
+        <v>14</v>
+      </c>
+      <c r="E266">
+        <v>88.4</v>
+      </c>
+      <c r="F266">
+        <v>149.1</v>
+      </c>
+      <c r="G266">
+        <v>68.5</v>
+      </c>
+      <c r="H266">
+        <v>121.7</v>
+      </c>
+      <c r="I266">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" t="s">
+        <v>9</v>
+      </c>
+      <c r="B267" t="s">
+        <v>85</v>
+      </c>
+      <c r="C267" t="s">
+        <v>36</v>
+      </c>
+      <c r="D267" t="s">
+        <v>37</v>
+      </c>
+      <c r="E267">
+        <v>100</v>
+      </c>
+      <c r="F267">
+        <v>131.5</v>
+      </c>
+      <c r="G267">
+        <v>31.5</v>
+      </c>
+      <c r="H267">
+        <v>121.7</v>
+      </c>
+      <c r="I267">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" t="s">
+        <v>9</v>
+      </c>
+      <c r="B268" t="s">
+        <v>85</v>
+      </c>
+      <c r="C268" t="s">
+        <v>33</v>
+      </c>
+      <c r="D268" t="s">
+        <v>54</v>
+      </c>
+      <c r="E268">
+        <v>167</v>
+      </c>
+      <c r="F268">
+        <v>216.4</v>
+      </c>
+      <c r="G268">
+        <v>29.5</v>
+      </c>
+      <c r="H268">
+        <v>121.7</v>
+      </c>
+      <c r="I268">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" t="s">
+        <v>9</v>
+      </c>
+      <c r="B269" t="s">
+        <v>85</v>
+      </c>
+      <c r="C269" t="s">
+        <v>33</v>
+      </c>
+      <c r="D269" t="s">
+        <v>34</v>
+      </c>
+      <c r="E269">
+        <v>109</v>
+      </c>
+      <c r="F269">
+        <v>138.8</v>
+      </c>
+      <c r="G269">
+        <v>27.3</v>
+      </c>
+      <c r="H269">
+        <v>121.7</v>
+      </c>
+      <c r="I269">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
+      <c r="A270" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" t="s">
+        <v>85</v>
+      </c>
+      <c r="C270" t="s">
+        <v>11</v>
+      </c>
+      <c r="D270" t="s">
+        <v>12</v>
+      </c>
+      <c r="E270">
+        <v>80.7</v>
+      </c>
+      <c r="F270">
+        <v>97.8</v>
+      </c>
+      <c r="G270">
+        <v>21.1</v>
+      </c>
+      <c r="H270" t="s">
+        <v>18</v>
+      </c>
+      <c r="I270" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" t="s">
+        <v>9</v>
+      </c>
+      <c r="B271" t="s">
+        <v>85</v>
+      </c>
+      <c r="C271" t="s">
+        <v>29</v>
+      </c>
+      <c r="D271" t="s">
+        <v>71</v>
+      </c>
+      <c r="E271">
+        <v>103.8</v>
+      </c>
+      <c r="F271">
+        <v>124.3</v>
+      </c>
+      <c r="G271">
+        <v>19.7</v>
+      </c>
+      <c r="H271">
+        <v>121.7</v>
+      </c>
+      <c r="I271">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9">
+      <c r="A272" t="s">
+        <v>9</v>
+      </c>
+      <c r="B272" t="s">
+        <v>85</v>
+      </c>
+      <c r="C272" t="s">
+        <v>45</v>
+      </c>
+      <c r="D272" t="s">
+        <v>49</v>
+      </c>
+      <c r="E272">
+        <v>88.4</v>
+      </c>
+      <c r="F272">
+        <v>104.5</v>
+      </c>
+      <c r="G272">
+        <v>18.1</v>
+      </c>
+      <c r="H272" t="s">
+        <v>18</v>
+      </c>
+      <c r="I272" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" t="s">
+        <v>9</v>
+      </c>
+      <c r="B273" t="s">
+        <v>85</v>
+      </c>
+      <c r="C273" t="s">
+        <v>21</v>
+      </c>
+      <c r="D273" t="s">
+        <v>70</v>
+      </c>
+      <c r="E273">
+        <v>92.3</v>
+      </c>
+      <c r="F273">
+        <v>108.4</v>
+      </c>
+      <c r="G273">
+        <v>17.5</v>
+      </c>
+      <c r="H273" t="s">
+        <v>18</v>
+      </c>
+      <c r="I273" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274" t="s">
+        <v>9</v>
+      </c>
+      <c r="B274" t="s">
+        <v>85</v>
+      </c>
+      <c r="C274" t="s">
+        <v>27</v>
+      </c>
+      <c r="D274" t="s">
+        <v>28</v>
+      </c>
+      <c r="E274">
+        <v>116.9</v>
+      </c>
+      <c r="F274">
+        <v>136.5</v>
+      </c>
+      <c r="G274">
+        <v>16.7</v>
+      </c>
+      <c r="H274">
+        <v>121.7</v>
+      </c>
+      <c r="I274">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275" t="s">
+        <v>9</v>
+      </c>
+      <c r="B275" t="s">
+        <v>85</v>
+      </c>
+      <c r="C275" t="s">
+        <v>36</v>
+      </c>
+      <c r="D275" t="s">
+        <v>55</v>
+      </c>
+      <c r="E275">
+        <v>115.3</v>
+      </c>
+      <c r="F275">
+        <v>134</v>
+      </c>
+      <c r="G275">
+        <v>16.2</v>
+      </c>
+      <c r="H275">
+        <v>121.7</v>
+      </c>
+      <c r="I275">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276" t="s">
+        <v>9</v>
+      </c>
+      <c r="B276" t="s">
+        <v>85</v>
+      </c>
+      <c r="C276" t="s">
+        <v>29</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276">
+        <v>100</v>
+      </c>
+      <c r="F276">
+        <v>112.6</v>
+      </c>
+      <c r="G276">
+        <v>12.6</v>
+      </c>
+      <c r="H276" t="s">
+        <v>18</v>
+      </c>
+      <c r="I276" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="A277" t="s">
+        <v>9</v>
+      </c>
+      <c r="B277" t="s">
+        <v>85</v>
+      </c>
+      <c r="C277" t="s">
+        <v>79</v>
+      </c>
+      <c r="D277" t="s">
+        <v>80</v>
+      </c>
+      <c r="E277">
+        <v>123</v>
+      </c>
+      <c r="F277">
+        <v>137.7</v>
+      </c>
+      <c r="G277">
+        <v>11.9</v>
+      </c>
+      <c r="H277">
+        <v>121.7</v>
+      </c>
+      <c r="I277">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="A278" t="s">
+        <v>9</v>
+      </c>
+      <c r="B278" t="s">
+        <v>85</v>
+      </c>
+      <c r="C278" t="s">
+        <v>60</v>
+      </c>
+      <c r="D278" t="s">
+        <v>61</v>
+      </c>
+      <c r="E278">
+        <v>155.8</v>
+      </c>
+      <c r="F278">
+        <v>173.7</v>
+      </c>
+      <c r="G278">
+        <v>11.5</v>
+      </c>
+      <c r="H278">
+        <v>121.7</v>
+      </c>
+      <c r="I278">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9">
+      <c r="A279" t="s">
+        <v>9</v>
+      </c>
+      <c r="B279" t="s">
+        <v>85</v>
+      </c>
+      <c r="C279" t="s">
+        <v>36</v>
+      </c>
+      <c r="D279" t="s">
+        <v>62</v>
+      </c>
+      <c r="E279">
+        <v>126.9</v>
+      </c>
+      <c r="F279">
+        <v>141.5</v>
+      </c>
+      <c r="G279">
+        <v>11.5</v>
+      </c>
+      <c r="H279">
+        <v>121.7</v>
+      </c>
+      <c r="I279">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9">
+      <c r="A280" t="s">
+        <v>9</v>
+      </c>
+      <c r="B280" t="s">
+        <v>85</v>
+      </c>
+      <c r="C280" t="s">
+        <v>74</v>
+      </c>
+      <c r="D280" t="s">
+        <v>75</v>
+      </c>
+      <c r="E280">
+        <v>126.9</v>
+      </c>
+      <c r="F280">
+        <v>140.5</v>
+      </c>
+      <c r="G280">
+        <v>10.7</v>
+      </c>
+      <c r="H280">
+        <v>121.7</v>
+      </c>
+      <c r="I280">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9">
+      <c r="A281" t="s">
+        <v>9</v>
+      </c>
+      <c r="B281" t="s">
+        <v>85</v>
+      </c>
+      <c r="C281" t="s">
+        <v>56</v>
+      </c>
+      <c r="D281" t="s">
+        <v>57</v>
+      </c>
+      <c r="E281">
+        <v>87.6</v>
+      </c>
+      <c r="F281">
+        <v>96.6</v>
+      </c>
+      <c r="G281">
+        <v>10.2</v>
+      </c>
+      <c r="H281" t="s">
+        <v>18</v>
+      </c>
+      <c r="I281" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9">
+      <c r="A282" t="s">
+        <v>9</v>
+      </c>
+      <c r="B282" t="s">
+        <v>85</v>
+      </c>
+      <c r="C282" t="s">
+        <v>11</v>
+      </c>
+      <c r="D282" t="s">
+        <v>53</v>
+      </c>
+      <c r="E282">
+        <v>92.3</v>
+      </c>
+      <c r="F282">
+        <v>101.6</v>
+      </c>
+      <c r="G282">
+        <v>10.1</v>
+      </c>
+      <c r="H282" t="s">
+        <v>18</v>
+      </c>
+      <c r="I282" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9">
+      <c r="A283" t="s">
+        <v>9</v>
+      </c>
+      <c r="B283" t="s">
+        <v>85</v>
+      </c>
+      <c r="C283" t="s">
+        <v>51</v>
+      </c>
+      <c r="D283" t="s">
+        <v>52</v>
+      </c>
+      <c r="E283">
+        <v>138.4</v>
+      </c>
+      <c r="F283">
+        <v>151.7</v>
+      </c>
+      <c r="G283">
+        <v>9.5</v>
+      </c>
+      <c r="H283">
+        <v>121.7</v>
+      </c>
+      <c r="I283">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9">
+      <c r="A284" t="s">
+        <v>9</v>
+      </c>
+      <c r="B284" t="s">
+        <v>85</v>
+      </c>
+      <c r="C284" t="s">
+        <v>43</v>
+      </c>
+      <c r="D284" t="s">
+        <v>44</v>
+      </c>
+      <c r="E284">
+        <v>126.9</v>
+      </c>
+      <c r="F284">
+        <v>138</v>
+      </c>
+      <c r="G284">
+        <v>8.7</v>
+      </c>
+      <c r="H284">
+        <v>121.7</v>
+      </c>
+      <c r="I284">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9">
+      <c r="A285" t="s">
+        <v>9</v>
+      </c>
+      <c r="B285" t="s">
+        <v>85</v>
+      </c>
+      <c r="C285" t="s">
+        <v>43</v>
+      </c>
+      <c r="D285" t="s">
+        <v>64</v>
+      </c>
+      <c r="E285">
+        <v>143.2</v>
+      </c>
+      <c r="F285">
+        <v>150.2</v>
+      </c>
+      <c r="G285">
+        <v>4.8</v>
+      </c>
+      <c r="H285">
+        <v>121.7</v>
+      </c>
+      <c r="I285">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9">
+      <c r="A286" t="s">
+        <v>9</v>
+      </c>
+      <c r="B286" t="s">
+        <v>85</v>
+      </c>
+      <c r="C286" t="s">
+        <v>36</v>
+      </c>
+      <c r="D286" t="s">
+        <v>66</v>
+      </c>
+      <c r="E286">
+        <v>155.5</v>
+      </c>
+      <c r="F286">
+        <v>161.9</v>
+      </c>
+      <c r="G286">
+        <v>4.1</v>
+      </c>
+      <c r="H286">
+        <v>121.7</v>
+      </c>
+      <c r="I286">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9">
+      <c r="A287" t="s">
+        <v>9</v>
+      </c>
+      <c r="B287" t="s">
+        <v>85</v>
+      </c>
+      <c r="C287" t="s">
+        <v>43</v>
+      </c>
+      <c r="D287" t="s">
+        <v>58</v>
+      </c>
+      <c r="E287">
+        <v>135.2</v>
+      </c>
+      <c r="F287">
+        <v>138.8</v>
+      </c>
+      <c r="G287">
+        <v>2.6</v>
+      </c>
+      <c r="H287">
+        <v>121.7</v>
+      </c>
+      <c r="I287">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9">
+      <c r="A288" t="s">
+        <v>9</v>
+      </c>
+      <c r="B288" t="s">
+        <v>85</v>
+      </c>
+      <c r="C288" t="s">
+        <v>13</v>
+      </c>
+      <c r="D288" t="s">
+        <v>65</v>
+      </c>
+      <c r="E288">
+        <v>134.6</v>
+      </c>
+      <c r="F288">
+        <v>136.8</v>
+      </c>
+      <c r="G288">
+        <v>1.6</v>
+      </c>
+      <c r="H288">
+        <v>121.7</v>
+      </c>
+      <c r="I288">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="A289" t="s">
+        <v>9</v>
+      </c>
+      <c r="B289" t="s">
+        <v>86</v>
+      </c>
+      <c r="C289" t="s">
+        <v>13</v>
+      </c>
+      <c r="D289" t="s">
+        <v>14</v>
+      </c>
+      <c r="E289">
+        <v>88.4</v>
+      </c>
+      <c r="F289">
+        <v>150.2</v>
+      </c>
+      <c r="G289">
+        <v>69.8</v>
+      </c>
+      <c r="H289">
+        <v>121.8</v>
+      </c>
+      <c r="I289">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9">
+      <c r="A290" t="s">
+        <v>9</v>
+      </c>
+      <c r="B290" t="s">
+        <v>86</v>
+      </c>
+      <c r="C290" t="s">
+        <v>36</v>
+      </c>
+      <c r="D290" t="s">
+        <v>37</v>
+      </c>
+      <c r="E290">
+        <v>100</v>
+      </c>
+      <c r="F290">
+        <v>131.4</v>
+      </c>
+      <c r="G290">
+        <v>31.4</v>
+      </c>
+      <c r="H290">
+        <v>121.8</v>
+      </c>
+      <c r="I290">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9">
+      <c r="A291" t="s">
+        <v>9</v>
+      </c>
+      <c r="B291" t="s">
+        <v>86</v>
+      </c>
+      <c r="C291" t="s">
+        <v>33</v>
+      </c>
+      <c r="D291" t="s">
+        <v>54</v>
+      </c>
+      <c r="E291">
+        <v>167</v>
+      </c>
+      <c r="F291">
+        <v>218.5</v>
+      </c>
+      <c r="G291">
+        <v>30.8</v>
+      </c>
+      <c r="H291">
+        <v>121.8</v>
+      </c>
+      <c r="I291">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9">
+      <c r="A292" t="s">
+        <v>9</v>
+      </c>
+      <c r="B292" t="s">
+        <v>86</v>
+      </c>
+      <c r="C292" t="s">
+        <v>33</v>
+      </c>
+      <c r="D292" t="s">
+        <v>34</v>
+      </c>
+      <c r="E292">
+        <v>109</v>
+      </c>
+      <c r="F292">
+        <v>139.7</v>
+      </c>
+      <c r="G292">
+        <v>28.1</v>
+      </c>
+      <c r="H292">
+        <v>121.8</v>
+      </c>
+      <c r="I292">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9">
+      <c r="A293" t="s">
+        <v>9</v>
+      </c>
+      <c r="B293" t="s">
+        <v>86</v>
+      </c>
+      <c r="C293" t="s">
+        <v>29</v>
+      </c>
+      <c r="D293" t="s">
+        <v>71</v>
+      </c>
+      <c r="E293">
+        <v>103.8</v>
+      </c>
+      <c r="F293">
+        <v>125.6</v>
+      </c>
+      <c r="G293">
+        <v>20.9</v>
+      </c>
+      <c r="H293">
+        <v>121.8</v>
+      </c>
+      <c r="I293">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9">
+      <c r="A294" t="s">
+        <v>9</v>
+      </c>
+      <c r="B294" t="s">
+        <v>86</v>
+      </c>
+      <c r="C294" t="s">
+        <v>45</v>
+      </c>
+      <c r="D294" t="s">
+        <v>49</v>
+      </c>
+      <c r="E294">
+        <v>88.4</v>
+      </c>
+      <c r="F294">
+        <v>104.3</v>
+      </c>
+      <c r="G294">
+        <v>17.9</v>
+      </c>
+      <c r="H294" t="s">
+        <v>18</v>
+      </c>
+      <c r="I294" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9">
+      <c r="A295" t="s">
+        <v>9</v>
+      </c>
+      <c r="B295" t="s">
+        <v>86</v>
+      </c>
+      <c r="C295" t="s">
+        <v>27</v>
+      </c>
+      <c r="D295" t="s">
+        <v>28</v>
+      </c>
+      <c r="E295">
+        <v>116.9</v>
+      </c>
+      <c r="F295">
+        <v>137.1</v>
+      </c>
+      <c r="G295">
+        <v>17.2</v>
+      </c>
+      <c r="H295">
+        <v>121.8</v>
+      </c>
+      <c r="I295">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9">
+      <c r="A296" t="s">
+        <v>9</v>
+      </c>
+      <c r="B296" t="s">
+        <v>86</v>
+      </c>
+      <c r="C296" t="s">
+        <v>21</v>
+      </c>
+      <c r="D296" t="s">
+        <v>70</v>
+      </c>
+      <c r="E296">
+        <v>92.3</v>
+      </c>
+      <c r="F296">
+        <v>108</v>
+      </c>
+      <c r="G296">
+        <v>17</v>
+      </c>
+      <c r="H296" t="s">
+        <v>18</v>
+      </c>
+      <c r="I296" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9">
+      <c r="A297" t="s">
+        <v>9</v>
+      </c>
+      <c r="B297" t="s">
+        <v>86</v>
+      </c>
+      <c r="C297" t="s">
+        <v>36</v>
+      </c>
+      <c r="D297" t="s">
+        <v>55</v>
+      </c>
+      <c r="E297">
+        <v>115.3</v>
+      </c>
+      <c r="F297">
+        <v>134.5</v>
+      </c>
+      <c r="G297">
+        <v>16.5</v>
+      </c>
+      <c r="H297">
+        <v>121.8</v>
+      </c>
+      <c r="I297">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9">
+      <c r="A298" t="s">
+        <v>9</v>
+      </c>
+      <c r="B298" t="s">
+        <v>86</v>
+      </c>
+      <c r="C298" t="s">
+        <v>79</v>
+      </c>
+      <c r="D298" t="s">
+        <v>80</v>
+      </c>
+      <c r="E298">
+        <v>123</v>
+      </c>
+      <c r="F298">
+        <v>138.1</v>
+      </c>
+      <c r="G298">
+        <v>12.2</v>
+      </c>
+      <c r="H298">
+        <v>121.8</v>
+      </c>
+      <c r="I298">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9">
+      <c r="A299" t="s">
+        <v>9</v>
+      </c>
+      <c r="B299" t="s">
+        <v>86</v>
+      </c>
+      <c r="C299" t="s">
+        <v>60</v>
+      </c>
+      <c r="D299" t="s">
+        <v>61</v>
+      </c>
+      <c r="E299">
+        <v>155.8</v>
+      </c>
+      <c r="F299">
+        <v>173.8</v>
+      </c>
+      <c r="G299">
+        <v>11.5</v>
+      </c>
+      <c r="H299">
+        <v>121.8</v>
+      </c>
+      <c r="I299">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9">
+      <c r="A300" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" t="s">
+        <v>86</v>
+      </c>
+      <c r="C300" t="s">
+        <v>74</v>
+      </c>
+      <c r="D300" t="s">
+        <v>75</v>
+      </c>
+      <c r="E300">
+        <v>126.9</v>
+      </c>
+      <c r="F300">
+        <v>140.2</v>
+      </c>
+      <c r="G300">
+        <v>10.4</v>
+      </c>
+      <c r="H300">
+        <v>121.8</v>
+      </c>
+      <c r="I300">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9">
+      <c r="A301" t="s">
+        <v>9</v>
+      </c>
+      <c r="B301" t="s">
+        <v>86</v>
+      </c>
+      <c r="C301" t="s">
+        <v>51</v>
+      </c>
+      <c r="D301" t="s">
+        <v>52</v>
+      </c>
+      <c r="E301">
+        <v>138.4</v>
+      </c>
+      <c r="F301">
+        <v>152.6</v>
+      </c>
+      <c r="G301">
+        <v>10.2</v>
+      </c>
+      <c r="H301">
+        <v>121.8</v>
+      </c>
+      <c r="I301">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9">
+      <c r="A302" t="s">
+        <v>9</v>
+      </c>
+      <c r="B302" t="s">
+        <v>86</v>
+      </c>
+      <c r="C302" t="s">
+        <v>36</v>
+      </c>
+      <c r="D302" t="s">
+        <v>62</v>
+      </c>
+      <c r="E302">
+        <v>126.9</v>
+      </c>
+      <c r="F302">
+        <v>139.3</v>
+      </c>
+      <c r="G302">
+        <v>9.7</v>
+      </c>
+      <c r="H302">
+        <v>121.8</v>
+      </c>
+      <c r="I302">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9">
+      <c r="A303" t="s">
+        <v>9</v>
+      </c>
+      <c r="B303" t="s">
+        <v>86</v>
+      </c>
+      <c r="C303" t="s">
+        <v>43</v>
+      </c>
+      <c r="D303" t="s">
+        <v>44</v>
+      </c>
+      <c r="E303">
+        <v>126.9</v>
+      </c>
+      <c r="F303">
+        <v>136.7</v>
+      </c>
+      <c r="G303">
+        <v>7.7</v>
+      </c>
+      <c r="H303">
+        <v>121.8</v>
+      </c>
+      <c r="I303">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9">
+      <c r="A304" t="s">
+        <v>9</v>
+      </c>
+      <c r="B304" t="s">
+        <v>86</v>
+      </c>
+      <c r="C304" t="s">
+        <v>43</v>
+      </c>
+      <c r="D304" t="s">
+        <v>64</v>
+      </c>
+      <c r="E304">
+        <v>143.2</v>
+      </c>
+      <c r="F304">
+        <v>150.5</v>
+      </c>
+      <c r="G304">
+        <v>5</v>
+      </c>
+      <c r="H304">
+        <v>121.8</v>
+      </c>
+      <c r="I304">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9">
+      <c r="A305" t="s">
+        <v>9</v>
+      </c>
+      <c r="B305" t="s">
+        <v>86</v>
+      </c>
+      <c r="C305" t="s">
+        <v>36</v>
+      </c>
+      <c r="D305" t="s">
+        <v>66</v>
+      </c>
+      <c r="E305">
+        <v>155.5</v>
+      </c>
+      <c r="F305">
+        <v>161.7</v>
+      </c>
+      <c r="G305">
+        <v>4</v>
+      </c>
+      <c r="H305">
+        <v>121.8</v>
+      </c>
+      <c r="I305">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9">
+      <c r="A306" t="s">
+        <v>9</v>
+      </c>
+      <c r="B306" t="s">
+        <v>86</v>
+      </c>
+      <c r="C306" t="s">
+        <v>43</v>
+      </c>
+      <c r="D306" t="s">
+        <v>58</v>
+      </c>
+      <c r="E306">
+        <v>135.2</v>
+      </c>
+      <c r="F306">
+        <v>139.6</v>
+      </c>
+      <c r="G306">
+        <v>3.2</v>
+      </c>
+      <c r="H306">
+        <v>121.8</v>
+      </c>
+      <c r="I306">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9">
+      <c r="A307" t="s">
+        <v>9</v>
+      </c>
+      <c r="B307" t="s">
+        <v>86</v>
+      </c>
+      <c r="C307" t="s">
+        <v>13</v>
+      </c>
+      <c r="D307" t="s">
+        <v>65</v>
+      </c>
+      <c r="E307">
+        <v>134.6</v>
+      </c>
+      <c r="F307">
+        <v>136.3</v>
+      </c>
+      <c r="G307">
+        <v>1.3</v>
+      </c>
+      <c r="H307">
+        <v>121.8</v>
+      </c>
+      <c r="I307">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9">
+      <c r="A308" t="s">
+        <v>9</v>
+      </c>
+      <c r="B308" t="s">
+        <v>87</v>
+      </c>
+      <c r="C308" t="s">
+        <v>13</v>
+      </c>
+      <c r="D308" t="s">
+        <v>14</v>
+      </c>
+      <c r="E308">
+        <v>109.6</v>
+      </c>
+      <c r="F308">
+        <v>149.1</v>
+      </c>
+      <c r="G308">
+        <v>36</v>
+      </c>
+      <c r="H308">
+        <v>121.5</v>
+      </c>
+      <c r="I308">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9">
+      <c r="A309" t="s">
+        <v>9</v>
+      </c>
+      <c r="B309" t="s">
+        <v>87</v>
+      </c>
+      <c r="C309" t="s">
+        <v>33</v>
+      </c>
+      <c r="D309" t="s">
+        <v>54</v>
+      </c>
+      <c r="E309">
+        <v>167</v>
+      </c>
+      <c r="F309">
+        <v>219.9</v>
+      </c>
+      <c r="G309">
+        <v>31.6</v>
+      </c>
+      <c r="H309">
+        <v>121.5</v>
+      </c>
+      <c r="I309">
+        <v>80.9</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9">
+      <c r="A310" t="s">
+        <v>9</v>
+      </c>
+      <c r="B310" t="s">
+        <v>87</v>
+      </c>
+      <c r="C310" t="s">
+        <v>36</v>
+      </c>
+      <c r="D310" t="s">
+        <v>37</v>
+      </c>
+      <c r="E310">
+        <v>100</v>
+      </c>
+      <c r="F310">
+        <v>131.3</v>
+      </c>
+      <c r="G310">
+        <v>31.3</v>
+      </c>
+      <c r="H310">
+        <v>121.5</v>
+      </c>
+      <c r="I310">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9">
+      <c r="A311" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311" t="s">
+        <v>87</v>
+      </c>
+      <c r="C311" t="s">
+        <v>29</v>
+      </c>
+      <c r="D311" t="s">
+        <v>71</v>
+      </c>
+      <c r="E311">
+        <v>103.8</v>
+      </c>
+      <c r="F311">
+        <v>127.1</v>
+      </c>
+      <c r="G311">
+        <v>22.3</v>
+      </c>
+      <c r="H311">
+        <v>121.5</v>
+      </c>
+      <c r="I311">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9">
+      <c r="A312" t="s">
+        <v>9</v>
+      </c>
+      <c r="B312" t="s">
+        <v>87</v>
+      </c>
+      <c r="C312" t="s">
+        <v>33</v>
+      </c>
+      <c r="D312" t="s">
+        <v>34</v>
+      </c>
+      <c r="E312">
+        <v>115.1</v>
+      </c>
+      <c r="F312">
+        <v>140.1</v>
+      </c>
+      <c r="G312">
+        <v>21.6</v>
+      </c>
+      <c r="H312">
+        <v>121.5</v>
+      </c>
+      <c r="I312">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9">
+      <c r="A313" t="s">
+        <v>9</v>
+      </c>
+      <c r="B313" t="s">
+        <v>87</v>
+      </c>
+      <c r="C313" t="s">
+        <v>45</v>
+      </c>
+      <c r="D313" t="s">
+        <v>49</v>
+      </c>
+      <c r="E313">
+        <v>88.4</v>
+      </c>
+      <c r="F313">
+        <v>104.7</v>
+      </c>
+      <c r="G313">
+        <v>18.3</v>
+      </c>
+      <c r="H313" t="s">
+        <v>18</v>
+      </c>
+      <c r="I313" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9">
+      <c r="A314" t="s">
+        <v>9</v>
+      </c>
+      <c r="B314" t="s">
+        <v>87</v>
+      </c>
+      <c r="C314" t="s">
+        <v>27</v>
+      </c>
+      <c r="D314" t="s">
+        <v>28</v>
+      </c>
+      <c r="E314">
+        <v>116.9</v>
+      </c>
+      <c r="F314">
+        <v>138.2</v>
+      </c>
+      <c r="G314">
+        <v>18.2</v>
+      </c>
+      <c r="H314">
+        <v>121.5</v>
+      </c>
+      <c r="I314">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9">
+      <c r="A315" t="s">
+        <v>9</v>
+      </c>
+      <c r="B315" t="s">
+        <v>87</v>
+      </c>
+      <c r="C315" t="s">
+        <v>36</v>
+      </c>
+      <c r="D315" t="s">
+        <v>55</v>
+      </c>
+      <c r="E315">
+        <v>115.3</v>
+      </c>
+      <c r="F315">
+        <v>134.4</v>
+      </c>
+      <c r="G315">
+        <v>16.5</v>
+      </c>
+      <c r="H315">
+        <v>121.5</v>
+      </c>
+      <c r="I315">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9">
+      <c r="A316" t="s">
+        <v>9</v>
+      </c>
+      <c r="B316" t="s">
+        <v>87</v>
+      </c>
+      <c r="C316" t="s">
+        <v>21</v>
+      </c>
+      <c r="D316" t="s">
+        <v>70</v>
+      </c>
+      <c r="E316">
+        <v>92.3</v>
+      </c>
+      <c r="F316">
+        <v>106.3</v>
+      </c>
+      <c r="G316">
+        <v>15.1</v>
+      </c>
+      <c r="H316" t="s">
+        <v>18</v>
+      </c>
+      <c r="I316" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9">
+      <c r="A317" t="s">
+        <v>9</v>
+      </c>
+      <c r="B317" t="s">
+        <v>87</v>
+      </c>
+      <c r="C317" t="s">
+        <v>79</v>
+      </c>
+      <c r="D317" t="s">
+        <v>80</v>
+      </c>
+      <c r="E317">
+        <v>123</v>
+      </c>
+      <c r="F317">
+        <v>138.1</v>
+      </c>
+      <c r="G317">
+        <v>12.2</v>
+      </c>
+      <c r="H317">
+        <v>121.5</v>
+      </c>
+      <c r="I317">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9">
+      <c r="A318" t="s">
+        <v>9</v>
+      </c>
+      <c r="B318" t="s">
+        <v>87</v>
+      </c>
+      <c r="C318" t="s">
+        <v>51</v>
+      </c>
+      <c r="D318" t="s">
+        <v>52</v>
+      </c>
+      <c r="E318">
+        <v>138.4</v>
+      </c>
+      <c r="F318">
+        <v>154.4</v>
+      </c>
+      <c r="G318">
+        <v>11.5</v>
+      </c>
+      <c r="H318">
+        <v>121.5</v>
+      </c>
+      <c r="I318">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9">
+      <c r="A319" t="s">
+        <v>9</v>
+      </c>
+      <c r="B319" t="s">
+        <v>87</v>
+      </c>
+      <c r="C319" t="s">
+        <v>60</v>
+      </c>
+      <c r="D319" t="s">
+        <v>61</v>
+      </c>
+      <c r="E319">
+        <v>155.8</v>
+      </c>
+      <c r="F319">
+        <v>173.2</v>
+      </c>
+      <c r="G319">
+        <v>11.1</v>
+      </c>
+      <c r="H319">
+        <v>121.5</v>
+      </c>
+      <c r="I319">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9">
+      <c r="A320" t="s">
+        <v>9</v>
+      </c>
+      <c r="B320" t="s">
+        <v>87</v>
+      </c>
+      <c r="C320" t="s">
+        <v>74</v>
+      </c>
+      <c r="D320" t="s">
+        <v>75</v>
+      </c>
+      <c r="E320">
+        <v>126.9</v>
+      </c>
+      <c r="F320">
+        <v>140.2</v>
+      </c>
+      <c r="G320">
+        <v>10.4</v>
+      </c>
+      <c r="H320">
+        <v>121.5</v>
+      </c>
+      <c r="I320">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9">
+      <c r="A321" t="s">
+        <v>9</v>
+      </c>
+      <c r="B321" t="s">
+        <v>87</v>
+      </c>
+      <c r="C321" t="s">
+        <v>36</v>
+      </c>
+      <c r="D321" t="s">
+        <v>62</v>
+      </c>
+      <c r="E321">
+        <v>126.9</v>
+      </c>
+      <c r="F321">
+        <v>137.5</v>
+      </c>
+      <c r="G321">
+        <v>8.3</v>
+      </c>
+      <c r="H321">
+        <v>121.5</v>
+      </c>
+      <c r="I321">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9">
+      <c r="A322" t="s">
+        <v>9</v>
+      </c>
+      <c r="B322" t="s">
+        <v>87</v>
+      </c>
+      <c r="C322" t="s">
+        <v>43</v>
+      </c>
+      <c r="D322" t="s">
+        <v>44</v>
+      </c>
+      <c r="E322">
+        <v>126.9</v>
+      </c>
+      <c r="F322">
+        <v>136.4</v>
+      </c>
+      <c r="G322">
+        <v>7.5</v>
+      </c>
+      <c r="H322">
+        <v>121.5</v>
+      </c>
+      <c r="I322">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9">
+      <c r="A323" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" t="s">
+        <v>87</v>
+      </c>
+      <c r="C323" t="s">
+        <v>43</v>
+      </c>
+      <c r="D323" t="s">
+        <v>64</v>
+      </c>
+      <c r="E323">
+        <v>143.2</v>
+      </c>
+      <c r="F323">
+        <v>150</v>
+      </c>
+      <c r="G323">
+        <v>4.7</v>
+      </c>
+      <c r="H323">
+        <v>121.5</v>
+      </c>
+      <c r="I323">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9">
+      <c r="A324" t="s">
+        <v>9</v>
+      </c>
+      <c r="B324" t="s">
+        <v>87</v>
+      </c>
+      <c r="C324" t="s">
+        <v>43</v>
+      </c>
+      <c r="D324" t="s">
+        <v>58</v>
+      </c>
+      <c r="E324">
+        <v>135.2</v>
+      </c>
+      <c r="F324">
+        <v>140.7</v>
+      </c>
+      <c r="G324">
+        <v>4.1</v>
+      </c>
+      <c r="H324">
+        <v>121.5</v>
+      </c>
+      <c r="I324">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9">
+      <c r="A325" t="s">
+        <v>9</v>
+      </c>
+      <c r="B325" t="s">
+        <v>87</v>
+      </c>
+      <c r="C325" t="s">
+        <v>36</v>
+      </c>
+      <c r="D325" t="s">
+        <v>66</v>
+      </c>
+      <c r="E325">
+        <v>155.5</v>
+      </c>
+      <c r="F325">
+        <v>161</v>
+      </c>
+      <c r="G325">
+        <v>3.5</v>
+      </c>
+      <c r="H325">
+        <v>121.5</v>
+      </c>
+      <c r="I325">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9">
+      <c r="A326" t="s">
+        <v>9</v>
+      </c>
+      <c r="B326" t="s">
+        <v>87</v>
+      </c>
+      <c r="C326" t="s">
+        <v>13</v>
+      </c>
+      <c r="D326" t="s">
+        <v>65</v>
+      </c>
+      <c r="E326">
+        <v>134.6</v>
+      </c>
+      <c r="F326">
+        <v>136.3</v>
+      </c>
+      <c r="G326">
+        <v>1.2</v>
+      </c>
+      <c r="H326">
+        <v>121.5</v>
+      </c>
+      <c r="I326">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9">
+      <c r="A327" t="s">
+        <v>9</v>
+      </c>
+      <c r="B327" t="s">
+        <v>87</v>
+      </c>
+      <c r="C327" t="s">
+        <v>77</v>
+      </c>
+      <c r="D327" t="s">
+        <v>78</v>
+      </c>
+      <c r="E327">
+        <v>138.4</v>
+      </c>
+      <c r="F327">
+        <v>133.8</v>
+      </c>
+      <c r="G327">
+        <v>-3.2</v>
+      </c>
+      <c r="H327">
+        <v>121.5</v>
+      </c>
+      <c r="I327">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9">
+      <c r="A328" t="s">
+        <v>9</v>
+      </c>
+      <c r="B328" t="s">
+        <v>88</v>
+      </c>
+      <c r="C328" t="s">
+        <v>13</v>
+      </c>
+      <c r="D328" t="s">
+        <v>14</v>
+      </c>
+      <c r="E328">
+        <v>109.6</v>
+      </c>
+      <c r="F328">
+        <v>147.2</v>
+      </c>
+      <c r="G328">
+        <v>34.3</v>
+      </c>
+      <c r="H328">
+        <v>121.2</v>
+      </c>
+      <c r="I328">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9">
+      <c r="A329" t="s">
+        <v>9</v>
+      </c>
+      <c r="B329" t="s">
+        <v>88</v>
+      </c>
+      <c r="C329" t="s">
+        <v>33</v>
+      </c>
+      <c r="D329" t="s">
+        <v>54</v>
+      </c>
+      <c r="E329">
+        <v>167</v>
+      </c>
+      <c r="F329">
+        <v>219.7</v>
+      </c>
+      <c r="G329">
+        <v>31.5</v>
+      </c>
+      <c r="H329">
+        <v>121.2</v>
+      </c>
+      <c r="I329">
+        <v>81.2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9">
+      <c r="A330" t="s">
+        <v>9</v>
+      </c>
+      <c r="B330" t="s">
+        <v>88</v>
+      </c>
+      <c r="C330" t="s">
+        <v>36</v>
+      </c>
+      <c r="D330" t="s">
+        <v>37</v>
+      </c>
+      <c r="E330">
+        <v>100</v>
+      </c>
+      <c r="F330">
+        <v>130.4</v>
+      </c>
+      <c r="G330">
+        <v>30.4</v>
+      </c>
+      <c r="H330">
+        <v>121.2</v>
+      </c>
+      <c r="I330">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9">
+      <c r="A331" t="s">
+        <v>9</v>
+      </c>
+      <c r="B331" t="s">
+        <v>88</v>
+      </c>
+      <c r="C331" t="s">
+        <v>29</v>
+      </c>
+      <c r="D331" t="s">
+        <v>71</v>
+      </c>
+      <c r="E331">
+        <v>103.8</v>
+      </c>
+      <c r="F331">
+        <v>127.7</v>
+      </c>
+      <c r="G331">
+        <v>23</v>
+      </c>
+      <c r="H331">
+        <v>121.2</v>
+      </c>
+      <c r="I331">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9">
+      <c r="A332" t="s">
+        <v>9</v>
+      </c>
+      <c r="B332" t="s">
+        <v>88</v>
+      </c>
+      <c r="C332" t="s">
+        <v>33</v>
+      </c>
+      <c r="D332" t="s">
+        <v>34</v>
+      </c>
+      <c r="E332">
+        <v>115.1</v>
+      </c>
+      <c r="F332">
+        <v>138.9</v>
+      </c>
+      <c r="G332">
+        <v>20.6</v>
+      </c>
+      <c r="H332">
+        <v>121.2</v>
+      </c>
+      <c r="I332">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9">
+      <c r="A333" t="s">
+        <v>9</v>
+      </c>
+      <c r="B333" t="s">
+        <v>88</v>
+      </c>
+      <c r="C333" t="s">
+        <v>45</v>
+      </c>
+      <c r="D333" t="s">
+        <v>49</v>
+      </c>
+      <c r="E333">
+        <v>88.4</v>
+      </c>
+      <c r="F333">
+        <v>104.9</v>
+      </c>
+      <c r="G333">
+        <v>18.6</v>
+      </c>
+      <c r="H333" t="s">
+        <v>18</v>
+      </c>
+      <c r="I333" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9">
+      <c r="A334" t="s">
+        <v>9</v>
+      </c>
+      <c r="B334" t="s">
+        <v>88</v>
+      </c>
+      <c r="C334" t="s">
+        <v>27</v>
+      </c>
+      <c r="D334" t="s">
+        <v>28</v>
+      </c>
+      <c r="E334">
+        <v>116.9</v>
+      </c>
+      <c r="F334">
+        <v>138.7</v>
+      </c>
+      <c r="G334">
+        <v>18.6</v>
+      </c>
+      <c r="H334">
+        <v>121.2</v>
+      </c>
+      <c r="I334">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9">
+      <c r="A335" t="s">
+        <v>9</v>
+      </c>
+      <c r="B335" t="s">
+        <v>88</v>
+      </c>
+      <c r="C335" t="s">
+        <v>36</v>
+      </c>
+      <c r="D335" t="s">
+        <v>55</v>
+      </c>
+      <c r="E335">
+        <v>115.3</v>
+      </c>
+      <c r="F335">
+        <v>134.4</v>
+      </c>
+      <c r="G335">
+        <v>16.4</v>
+      </c>
+      <c r="H335">
+        <v>121.2</v>
+      </c>
+      <c r="I335">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9">
+      <c r="A336" t="s">
+        <v>9</v>
+      </c>
+      <c r="B336" t="s">
+        <v>88</v>
+      </c>
+      <c r="C336" t="s">
+        <v>21</v>
+      </c>
+      <c r="D336" t="s">
+        <v>70</v>
+      </c>
+      <c r="E336">
+        <v>92.3</v>
+      </c>
+      <c r="F336">
+        <v>105.3</v>
+      </c>
+      <c r="G336">
+        <v>14</v>
+      </c>
+      <c r="H336" t="s">
+        <v>18</v>
+      </c>
+      <c r="I336" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9">
+      <c r="A337" t="s">
+        <v>9</v>
+      </c>
+      <c r="B337" t="s">
+        <v>88</v>
+      </c>
+      <c r="C337" t="s">
+        <v>51</v>
+      </c>
+      <c r="D337" t="s">
+        <v>52</v>
+      </c>
+      <c r="E337">
+        <v>138.4</v>
+      </c>
+      <c r="F337">
+        <v>155.6</v>
+      </c>
+      <c r="G337">
+        <v>12.4</v>
+      </c>
+      <c r="H337">
+        <v>121.2</v>
+      </c>
+      <c r="I337">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9">
+      <c r="A338" t="s">
+        <v>9</v>
+      </c>
+      <c r="B338" t="s">
+        <v>88</v>
+      </c>
+      <c r="C338" t="s">
+        <v>16</v>
+      </c>
+      <c r="D338" t="s">
+        <v>89</v>
+      </c>
+      <c r="E338">
+        <v>115.3</v>
+      </c>
+      <c r="F338">
+        <v>127.8</v>
+      </c>
+      <c r="G338">
+        <v>10.8</v>
+      </c>
+      <c r="H338">
+        <v>121.2</v>
+      </c>
+      <c r="I338">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9">
+      <c r="A339" t="s">
+        <v>9</v>
+      </c>
+      <c r="B339" t="s">
+        <v>88</v>
+      </c>
+      <c r="C339" t="s">
+        <v>60</v>
+      </c>
+      <c r="D339" t="s">
+        <v>61</v>
+      </c>
+      <c r="E339">
+        <v>155.8</v>
+      </c>
+      <c r="F339">
+        <v>171.8</v>
+      </c>
+      <c r="G339">
+        <v>10.3</v>
+      </c>
+      <c r="H339">
+        <v>121.2</v>
+      </c>
+      <c r="I339">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9">
+      <c r="A340" t="s">
+        <v>9</v>
+      </c>
+      <c r="B340" t="s">
+        <v>88</v>
+      </c>
+      <c r="C340" t="s">
+        <v>74</v>
+      </c>
+      <c r="D340" t="s">
+        <v>75</v>
+      </c>
+      <c r="E340">
+        <v>126.9</v>
+      </c>
+      <c r="F340">
+        <v>139.2</v>
+      </c>
+      <c r="G340">
+        <v>9.6</v>
+      </c>
+      <c r="H340">
+        <v>121.2</v>
+      </c>
+      <c r="I340">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9">
+      <c r="A341" t="s">
+        <v>9</v>
+      </c>
+      <c r="B341" t="s">
+        <v>88</v>
+      </c>
+      <c r="C341" t="s">
+        <v>36</v>
+      </c>
+      <c r="D341" t="s">
+        <v>62</v>
+      </c>
+      <c r="E341">
+        <v>126.9</v>
+      </c>
+      <c r="F341">
+        <v>136.1</v>
+      </c>
+      <c r="G341">
+        <v>7.2</v>
+      </c>
+      <c r="H341">
+        <v>121.2</v>
+      </c>
+      <c r="I341">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9">
+      <c r="A342" t="s">
+        <v>9</v>
+      </c>
+      <c r="B342" t="s">
+        <v>88</v>
+      </c>
+      <c r="C342" t="s">
+        <v>43</v>
+      </c>
+      <c r="D342" t="s">
+        <v>44</v>
+      </c>
+      <c r="E342">
+        <v>126.9</v>
+      </c>
+      <c r="F342">
+        <v>135.1</v>
+      </c>
+      <c r="G342">
+        <v>6.4</v>
+      </c>
+      <c r="H342">
+        <v>121.2</v>
+      </c>
+      <c r="I342">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9">
+      <c r="A343" t="s">
+        <v>9</v>
+      </c>
+      <c r="B343" t="s">
+        <v>88</v>
+      </c>
+      <c r="C343" t="s">
+        <v>43</v>
+      </c>
+      <c r="D343" t="s">
+        <v>58</v>
+      </c>
+      <c r="E343">
+        <v>135.2</v>
+      </c>
+      <c r="F343">
+        <v>142.5</v>
+      </c>
+      <c r="G343">
+        <v>5.4</v>
+      </c>
+      <c r="H343">
+        <v>121.2</v>
+      </c>
+      <c r="I343">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9">
+      <c r="A344" t="s">
+        <v>9</v>
+      </c>
+      <c r="B344" t="s">
+        <v>88</v>
+      </c>
+      <c r="C344" t="s">
+        <v>43</v>
+      </c>
+      <c r="D344" t="s">
+        <v>64</v>
+      </c>
+      <c r="E344">
+        <v>143.2</v>
+      </c>
+      <c r="F344">
+        <v>150.2</v>
+      </c>
+      <c r="G344">
+        <v>4.8</v>
+      </c>
+      <c r="H344">
+        <v>121.2</v>
+      </c>
+      <c r="I344">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9">
+      <c r="A345" t="s">
+        <v>9</v>
+      </c>
+      <c r="B345" t="s">
+        <v>88</v>
+      </c>
+      <c r="C345" t="s">
+        <v>79</v>
+      </c>
+      <c r="D345" t="s">
+        <v>80</v>
+      </c>
+      <c r="E345">
+        <v>134.6</v>
+      </c>
+      <c r="F345">
+        <v>138.4</v>
+      </c>
+      <c r="G345">
+        <v>2.8</v>
+      </c>
+      <c r="H345">
+        <v>121.2</v>
+      </c>
+      <c r="I345">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9">
+      <c r="A346" t="s">
+        <v>9</v>
+      </c>
+      <c r="B346" t="s">
+        <v>88</v>
+      </c>
+      <c r="C346" t="s">
+        <v>36</v>
+      </c>
+      <c r="D346" t="s">
+        <v>66</v>
+      </c>
+      <c r="E346">
+        <v>155.5</v>
+      </c>
+      <c r="F346">
+        <v>159.7</v>
+      </c>
+      <c r="G346">
+        <v>2.7</v>
+      </c>
+      <c r="H346">
+        <v>121.2</v>
+      </c>
+      <c r="I346">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9">
+      <c r="A347" t="s">
+        <v>9</v>
+      </c>
+      <c r="B347" t="s">
+        <v>88</v>
+      </c>
+      <c r="C347" t="s">
+        <v>13</v>
+      </c>
+      <c r="D347" t="s">
+        <v>65</v>
+      </c>
+      <c r="E347">
+        <v>134.6</v>
+      </c>
+      <c r="F347">
+        <v>135</v>
+      </c>
+      <c r="G347">
+        <v>0.3</v>
+      </c>
+      <c r="H347">
+        <v>121.2</v>
+      </c>
+      <c r="I347">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9">
+      <c r="A348" t="s">
+        <v>9</v>
+      </c>
+      <c r="B348" t="s">
+        <v>88</v>
+      </c>
+      <c r="C348" t="s">
+        <v>77</v>
+      </c>
+      <c r="D348" t="s">
+        <v>78</v>
+      </c>
+      <c r="E348">
+        <v>138.4</v>
+      </c>
+      <c r="F348">
+        <v>133.8</v>
+      </c>
+      <c r="G348">
+        <v>-3.2</v>
+      </c>
+      <c r="H348">
+        <v>121.2</v>
+      </c>
+      <c r="I348">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9">
+      <c r="A349" t="s">
+        <v>9</v>
+      </c>
+      <c r="B349" t="s">
+        <v>90</v>
+      </c>
+      <c r="C349" t="s">
+        <v>13</v>
+      </c>
+      <c r="D349" t="s">
+        <v>14</v>
+      </c>
+      <c r="E349">
+        <v>109.6</v>
+      </c>
+      <c r="F349">
+        <v>144.3</v>
+      </c>
+      <c r="G349">
+        <v>31.6</v>
+      </c>
+      <c r="H349">
+        <v>120.8</v>
+      </c>
+      <c r="I349">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9">
+      <c r="A350" t="s">
+        <v>9</v>
+      </c>
+      <c r="B350" t="s">
+        <v>90</v>
+      </c>
+      <c r="C350" t="s">
+        <v>33</v>
+      </c>
+      <c r="D350" t="s">
+        <v>54</v>
+      </c>
+      <c r="E350">
+        <v>167</v>
+      </c>
+      <c r="F350">
+        <v>219.7</v>
+      </c>
+      <c r="G350">
+        <v>31.5</v>
+      </c>
+      <c r="H350">
+        <v>120.8</v>
+      </c>
+      <c r="I350">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351" t="s">
+        <v>9</v>
+      </c>
+      <c r="B351" t="s">
+        <v>90</v>
+      </c>
+      <c r="C351" t="s">
+        <v>36</v>
+      </c>
+      <c r="D351" t="s">
+        <v>37</v>
+      </c>
+      <c r="E351">
+        <v>100</v>
+      </c>
+      <c r="F351">
+        <v>129.3</v>
+      </c>
+      <c r="G351">
+        <v>29.3</v>
+      </c>
+      <c r="H351">
+        <v>120.8</v>
+      </c>
+      <c r="I351">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352" t="s">
+        <v>9</v>
+      </c>
+      <c r="B352" t="s">
+        <v>90</v>
+      </c>
+      <c r="C352" t="s">
+        <v>29</v>
+      </c>
+      <c r="D352" t="s">
+        <v>71</v>
+      </c>
+      <c r="E352">
+        <v>103.8</v>
+      </c>
+      <c r="F352">
+        <v>128.3</v>
+      </c>
+      <c r="G352">
+        <v>23.5</v>
+      </c>
+      <c r="H352">
+        <v>120.8</v>
+      </c>
+      <c r="I352">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353" t="s">
+        <v>9</v>
+      </c>
+      <c r="B353" t="s">
+        <v>90</v>
+      </c>
+      <c r="C353" t="s">
+        <v>33</v>
+      </c>
+      <c r="D353" t="s">
+        <v>34</v>
+      </c>
+      <c r="E353">
+        <v>115.1</v>
+      </c>
+      <c r="F353">
+        <v>137</v>
+      </c>
+      <c r="G353">
+        <v>18.9</v>
+      </c>
+      <c r="H353">
+        <v>120.8</v>
+      </c>
+      <c r="I353">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9">
+      <c r="A354" t="s">
+        <v>9</v>
+      </c>
+      <c r="B354" t="s">
+        <v>90</v>
+      </c>
+      <c r="C354" t="s">
+        <v>27</v>
+      </c>
+      <c r="D354" t="s">
+        <v>28</v>
+      </c>
+      <c r="E354">
+        <v>116.9</v>
+      </c>
+      <c r="F354">
+        <v>138.8</v>
+      </c>
+      <c r="G354">
+        <v>18.6</v>
+      </c>
+      <c r="H354">
+        <v>120.8</v>
+      </c>
+      <c r="I354">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9">
+      <c r="A355" t="s">
+        <v>9</v>
+      </c>
+      <c r="B355" t="s">
+        <v>90</v>
+      </c>
+      <c r="C355" t="s">
+        <v>45</v>
+      </c>
+      <c r="D355" t="s">
+        <v>49</v>
+      </c>
+      <c r="E355">
+        <v>88.4</v>
+      </c>
+      <c r="F355">
+        <v>104.9</v>
+      </c>
+      <c r="G355">
+        <v>18.5</v>
+      </c>
+      <c r="H355" t="s">
+        <v>18</v>
+      </c>
+      <c r="I355" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9">
+      <c r="A356" t="s">
+        <v>9</v>
+      </c>
+      <c r="B356" t="s">
+        <v>90</v>
+      </c>
+      <c r="C356" t="s">
+        <v>36</v>
+      </c>
+      <c r="D356" t="s">
+        <v>55</v>
+      </c>
+      <c r="E356">
+        <v>115.3</v>
+      </c>
+      <c r="F356">
+        <v>133.7</v>
+      </c>
+      <c r="G356">
+        <v>15.9</v>
+      </c>
+      <c r="H356">
+        <v>120.8</v>
+      </c>
+      <c r="I356">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9">
+      <c r="A357" t="s">
+        <v>9</v>
+      </c>
+      <c r="B357" t="s">
+        <v>90</v>
+      </c>
+      <c r="C357" t="s">
+        <v>21</v>
+      </c>
+      <c r="D357" t="s">
+        <v>70</v>
+      </c>
+      <c r="E357">
+        <v>92.3</v>
+      </c>
+      <c r="F357">
+        <v>104.2</v>
+      </c>
+      <c r="G357">
+        <v>12.9</v>
+      </c>
+      <c r="H357" t="s">
+        <v>18</v>
+      </c>
+      <c r="I357" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9">
+      <c r="A358" t="s">
+        <v>9</v>
+      </c>
+      <c r="B358" t="s">
+        <v>90</v>
+      </c>
+      <c r="C358" t="s">
+        <v>51</v>
+      </c>
+      <c r="D358" t="s">
+        <v>52</v>
+      </c>
+      <c r="E358">
+        <v>138.4</v>
+      </c>
+      <c r="F358">
+        <v>155.7</v>
+      </c>
+      <c r="G358">
+        <v>12.4</v>
+      </c>
+      <c r="H358">
+        <v>120.8</v>
+      </c>
+      <c r="I358">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9">
+      <c r="A359" t="s">
+        <v>9</v>
+      </c>
+      <c r="B359" t="s">
+        <v>90</v>
+      </c>
+      <c r="C359" t="s">
+        <v>60</v>
+      </c>
+      <c r="D359" t="s">
+        <v>61</v>
+      </c>
+      <c r="E359">
+        <v>155.8</v>
+      </c>
+      <c r="F359">
+        <v>170.7</v>
+      </c>
+      <c r="G359">
+        <v>9.5</v>
+      </c>
+      <c r="H359">
+        <v>120.8</v>
+      </c>
+      <c r="I359">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9">
+      <c r="A360" t="s">
+        <v>9</v>
+      </c>
+      <c r="B360" t="s">
+        <v>90</v>
+      </c>
+      <c r="C360" t="s">
+        <v>74</v>
+      </c>
+      <c r="D360" t="s">
+        <v>75</v>
+      </c>
+      <c r="E360">
+        <v>126.9</v>
+      </c>
+      <c r="F360">
+        <v>138.8</v>
+      </c>
+      <c r="G360">
+        <v>9.3</v>
+      </c>
+      <c r="H360">
+        <v>120.8</v>
+      </c>
+      <c r="I360">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9">
+      <c r="A361" t="s">
+        <v>9</v>
+      </c>
+      <c r="B361" t="s">
+        <v>90</v>
+      </c>
+      <c r="C361" t="s">
+        <v>43</v>
+      </c>
+      <c r="D361" t="s">
+        <v>58</v>
+      </c>
+      <c r="E361">
+        <v>135.2</v>
+      </c>
+      <c r="F361">
+        <v>143.6</v>
+      </c>
+      <c r="G361">
+        <v>6.2</v>
+      </c>
+      <c r="H361">
+        <v>120.8</v>
+      </c>
+      <c r="I361">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9">
+      <c r="A362" t="s">
+        <v>9</v>
+      </c>
+      <c r="B362" t="s">
+        <v>90</v>
+      </c>
+      <c r="C362" t="s">
+        <v>36</v>
+      </c>
+      <c r="D362" t="s">
+        <v>62</v>
+      </c>
+      <c r="E362">
+        <v>126.9</v>
+      </c>
+      <c r="F362">
+        <v>133.1</v>
+      </c>
+      <c r="G362">
+        <v>4.8</v>
+      </c>
+      <c r="H362">
+        <v>120.8</v>
+      </c>
+      <c r="I362">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9">
+      <c r="A363" t="s">
+        <v>9</v>
+      </c>
+      <c r="B363" t="s">
+        <v>90</v>
+      </c>
+      <c r="C363" t="s">
+        <v>43</v>
+      </c>
+      <c r="D363" t="s">
+        <v>64</v>
+      </c>
+      <c r="E363">
+        <v>143.2</v>
+      </c>
+      <c r="F363">
+        <v>150</v>
+      </c>
+      <c r="G363">
+        <v>4.7</v>
+      </c>
+      <c r="H363">
+        <v>120.8</v>
+      </c>
+      <c r="I363">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364" t="s">
+        <v>9</v>
+      </c>
+      <c r="B364" t="s">
+        <v>90</v>
+      </c>
+      <c r="C364" t="s">
+        <v>43</v>
+      </c>
+      <c r="D364" t="s">
+        <v>44</v>
+      </c>
+      <c r="E364">
+        <v>130.7</v>
+      </c>
+      <c r="F364">
+        <v>134.9</v>
+      </c>
+      <c r="G364">
+        <v>3.2</v>
+      </c>
+      <c r="H364">
+        <v>120.8</v>
+      </c>
+      <c r="I364">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365" t="s">
+        <v>9</v>
+      </c>
+      <c r="B365" t="s">
+        <v>90</v>
+      </c>
+      <c r="C365" t="s">
+        <v>79</v>
+      </c>
+      <c r="D365" t="s">
+        <v>80</v>
+      </c>
+      <c r="E365">
+        <v>134.6</v>
+      </c>
+      <c r="F365">
+        <v>137.8</v>
+      </c>
+      <c r="G365">
+        <v>2.3</v>
+      </c>
+      <c r="H365">
+        <v>120.8</v>
+      </c>
+      <c r="I365">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366" t="s">
+        <v>9</v>
+      </c>
+      <c r="B366" t="s">
+        <v>90</v>
+      </c>
+      <c r="C366" t="s">
+        <v>36</v>
+      </c>
+      <c r="D366" t="s">
+        <v>66</v>
+      </c>
+      <c r="E366">
+        <v>155.5</v>
+      </c>
+      <c r="F366">
+        <v>158.5</v>
+      </c>
+      <c r="G366">
+        <v>1.9</v>
+      </c>
+      <c r="H366">
+        <v>120.8</v>
+      </c>
+      <c r="I366">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367" t="s">
+        <v>9</v>
+      </c>
+      <c r="B367" t="s">
+        <v>90</v>
+      </c>
+      <c r="C367" t="s">
+        <v>13</v>
+      </c>
+      <c r="D367" t="s">
+        <v>65</v>
+      </c>
+      <c r="E367">
+        <v>134.6</v>
+      </c>
+      <c r="F367">
+        <v>134.6</v>
+      </c>
+      <c r="G367">
+        <v>0</v>
+      </c>
+      <c r="H367">
+        <v>120.8</v>
+      </c>
+      <c r="I367">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9">
+      <c r="A368" t="s">
+        <v>9</v>
+      </c>
+      <c r="B368" t="s">
+        <v>90</v>
+      </c>
+      <c r="C368" t="s">
+        <v>77</v>
+      </c>
+      <c r="D368" t="s">
+        <v>78</v>
+      </c>
+      <c r="E368">
+        <v>138.4</v>
+      </c>
+      <c r="F368">
+        <v>133.8</v>
+      </c>
+      <c r="G368">
+        <v>-3.2</v>
+      </c>
+      <c r="H368">
+        <v>120.8</v>
+      </c>
+      <c r="I368">
+        <v>10.7</v>
       </c>
     </row>
   </sheetData>

--- a/source/8、绩效异常岗位/3、倒包岗/倒包岗-6月.xlsx
+++ b/source/8、绩效异常岗位/3、倒包岗/倒包岗-6月.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I478"/>
+  <dimension ref="A1:I591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18596,6 +18596,4235 @@
         <v>11.1</v>
       </c>
     </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>167</v>
+      </c>
+      <c r="F479" t="n">
+        <v>220</v>
+      </c>
+      <c r="G479" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H479" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I479" t="n">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>100</v>
+      </c>
+      <c r="F480" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="G480" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H480" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I480" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="F481" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="G481" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H481" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I481" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>98</v>
+      </c>
+      <c r="F482" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="G482" t="n">
+        <v>22</v>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>武昌</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="F483" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="G483" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H483" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I483" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F484" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="G484" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H484" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I484" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F485" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="G485" t="n">
+        <v>16</v>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F486" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="G486" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H486" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I486" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="F487" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="G487" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H487" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I487" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="F488" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="G488" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H488" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I488" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="F489" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="G489" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H489" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I489" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F490" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="G490" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H490" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I490" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="F491" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="G491" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H491" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I491" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F492" t="n">
+        <v>139.3</v>
+      </c>
+      <c r="G492" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H492" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I492" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="F493" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="G493" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H493" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I493" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F494" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="G494" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H494" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I494" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>漯河</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F495" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="G495" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H495" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I495" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="F496" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="G496" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="H496" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I496" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>167</v>
+      </c>
+      <c r="F497" t="n">
+        <v>219.4</v>
+      </c>
+      <c r="G497" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="H497" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I497" t="n">
+        <v>82.40000000000001</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="F498" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="G498" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H498" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I498" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>98</v>
+      </c>
+      <c r="F499" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="G499" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>武昌</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="F500" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="G500" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H500" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I500" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F501" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="G501" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H501" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I501" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F502" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="G502" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F503" t="n">
+        <v>132</v>
+      </c>
+      <c r="G503" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H503" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I503" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F504" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="G504" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H504" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I504" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="F505" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="G505" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H505" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I505" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="F506" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="G506" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H506" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I506" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F507" t="n">
+        <v>148</v>
+      </c>
+      <c r="G507" t="n">
+        <v>7</v>
+      </c>
+      <c r="H507" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I507" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="F508" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="G508" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H508" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I508" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="F509" t="n">
+        <v>149</v>
+      </c>
+      <c r="G509" t="n">
+        <v>4</v>
+      </c>
+      <c r="H509" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F510" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="G510" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H510" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I510" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="F511" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H511" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I511" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F512" t="n">
+        <v>157</v>
+      </c>
+      <c r="G512" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H512" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I512" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>漯河</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F513" t="n">
+        <v>133</v>
+      </c>
+      <c r="G513" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H513" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I513" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="F514" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G514" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="H514" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I514" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="F515" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G515" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="H515" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I515" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>167</v>
+      </c>
+      <c r="F516" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="G516" t="n">
+        <v>31</v>
+      </c>
+      <c r="H516" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I516" t="n">
+        <v>82.09999999999999</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="F517" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="G517" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H517" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I517" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>武昌</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="F518" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="G518" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H518" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I518" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>98</v>
+      </c>
+      <c r="F519" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="G519" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F520" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="G520" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H520" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I520" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F521" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G521" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F522" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="G522" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H522" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I522" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F523" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="G523" t="n">
+        <v>13</v>
+      </c>
+      <c r="H523" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I523" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="F524" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="G524" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H524" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I524" t="n">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="F525" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="G525" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H525" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I525" t="n">
+        <v>40.3</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F526" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="G526" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H526" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I526" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="F527" t="n">
+        <v>137.7</v>
+      </c>
+      <c r="G527" t="n">
+        <v>7</v>
+      </c>
+      <c r="H527" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I527" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="F528" t="n">
+        <v>149.3</v>
+      </c>
+      <c r="G528" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H528" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I528" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F529" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="G529" t="n">
+        <v>3</v>
+      </c>
+      <c r="H529" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I529" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="F530" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="G530" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H530" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I530" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F531" t="n">
+        <v>157</v>
+      </c>
+      <c r="G531" t="n">
+        <v>1</v>
+      </c>
+      <c r="H531" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I531" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>漯河</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F532" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="G532" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H532" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I532" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="F533" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="G533" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="H533" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I533" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="F534" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="G534" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="H534" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I534" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>167</v>
+      </c>
+      <c r="F535" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="G535" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="H535" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I535" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="F536" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="G536" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H536" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I536" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>武昌</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="F537" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="G537" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H537" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I537" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>98</v>
+      </c>
+      <c r="F538" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="G538" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F539" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="G539" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H539" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I539" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F540" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="G540" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H540" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I540" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F541" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G541" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F542" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="G542" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H542" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I542" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="F543" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="G543" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H543" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I543" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F544" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="G544" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H544" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I544" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="F545" t="n">
+        <v>168.6</v>
+      </c>
+      <c r="G545" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H545" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I545" t="n">
+        <v>40.3</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="F546" t="n">
+        <v>137.6</v>
+      </c>
+      <c r="G546" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H546" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I546" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="F547" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="G547" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H547" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I547" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F548" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="G548" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H548" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I548" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="F549" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="G549" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H549" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I549" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F550" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="G550" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H550" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I550" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>漯河</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F551" t="n">
+        <v>133</v>
+      </c>
+      <c r="G551" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H551" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="F552" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="G552" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="H552" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I552" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="F553" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="G553" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H553" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="I553" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>167</v>
+      </c>
+      <c r="F554" t="n">
+        <v>218.2</v>
+      </c>
+      <c r="G554" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H554" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I554" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="F555" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="G555" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H555" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I555" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>武昌</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="F556" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="G556" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H556" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I556" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>98</v>
+      </c>
+      <c r="F557" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="G557" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F558" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G558" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H558" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I558" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F559" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="G559" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H559" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I559" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F560" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="G560" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F561" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="G561" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H561" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I561" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F562" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="G562" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H562" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I562" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="F563" t="n">
+        <v>168.6</v>
+      </c>
+      <c r="G563" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H563" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I563" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="F564" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="G564" t="n">
+        <v>8</v>
+      </c>
+      <c r="H564" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I564" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="F565" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="G565" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H565" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I565" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="F566" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="G566" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H566" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I566" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F567" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="G567" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H567" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I567" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="F568" t="n">
+        <v>133</v>
+      </c>
+      <c r="G568" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H568" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I568" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F569" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="G569" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H569" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I569" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>漯河</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F570" t="n">
+        <v>133</v>
+      </c>
+      <c r="G570" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H570" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I570" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="F571" t="n">
+        <v>135</v>
+      </c>
+      <c r="G571" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="H571" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I571" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="F572" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="G572" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="H572" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I572" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>167</v>
+      </c>
+      <c r="F573" t="n">
+        <v>217.6</v>
+      </c>
+      <c r="G573" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="H573" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I573" t="n">
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="F574" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="G574" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H574" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I574" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>武昌</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="F575" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="G575" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H575" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I575" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>100</v>
+      </c>
+      <c r="F576" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G576" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>临海</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F577" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="G577" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H577" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I577" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F578" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="G578" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H578" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I578" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F579" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="G579" t="n">
+        <v>12</v>
+      </c>
+      <c r="H579" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I579" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F580" t="n">
+        <v>99</v>
+      </c>
+      <c r="G580" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>东方天地港</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F581" t="n">
+        <v>151</v>
+      </c>
+      <c r="G581" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H581" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I581" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>黑龙江区</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="F582" t="n">
+        <v>158</v>
+      </c>
+      <c r="G582" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H582" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I582" t="n">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="F583" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="G583" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H583" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I583" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>四川区</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="F584" t="n">
+        <v>135</v>
+      </c>
+      <c r="G584" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H584" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I584" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="F585" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="G585" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H585" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I585" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F586" t="n">
+        <v>138</v>
+      </c>
+      <c r="G586" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H586" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I586" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="F587" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="G587" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H587" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I587" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F588" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="G588" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H588" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I588" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>漯河</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F589" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="G589" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H589" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I589" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="F590" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="G590" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="H590" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I590" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>倒包岗</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="F591" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="G591" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H591" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I591" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
